--- a/results/job_matches_2026-06-04.xlsx
+++ b/results/job_matches_2026-06-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,60 +573,60 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer IV</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bennett Family of Companies</t>
+          <t>Airlines Reporting Corporation (ARC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>McDonough, GA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Databricks</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ce5cf18206c40a5</t>
+          <t>https://www.indeed.com/viewjob?jk=98137df2f9a11a45</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer IV</t>
+          <t>Sr. AWS Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Airlines Reporting Corporation (ARC)</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Hadoop</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98137df2f9a11a45</t>
+          <t>https://www.indeed.com/viewjob?jk=d62532bd79c16947</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer II: Data Engineer</t>
+          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, ECS, RDS, Spark, PySpark</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=050f0fd35c93466d</t>
+          <t>https://www.indeed.com/viewjob?jk=b9f4e94883170da4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. AWS Data Engineer</t>
+          <t>Senior ETL Developer (Azure &amp; MDM/Reltio Focus)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Duncan, SC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Hadoop</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d62532bd79c16947</t>
+          <t>https://www.indeed.com/viewjob?jk=feaf489696c6ebd7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
+          <t>Senior AWS Engineer - ML</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9f4e94883170da4</t>
+          <t>https://www.indeed.com/viewjob?jk=e808d31f6fa032cf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Software Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, Glue, Redshift, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df1d581c54c146f2</t>
+          <t>https://www.indeed.com/viewjob?jk=ac18de92e2d0da2c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior ETL Developer (Azure &amp; MDM/Reltio Focus)</t>
+          <t>Senior Engineer - Data</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Duncan, SC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feaf489696c6ebd7</t>
+          <t>https://www.indeed.com/viewjob?jk=d784ad2795e0379d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior AWS Engineer - ML</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tunnl</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, RDS, Scala, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e808d31f6fa032cf</t>
+          <t>https://www.indeed.com/viewjob?jk=b66532c29a2d2fb3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Information Technology - BI Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TCC Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fishers, IN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac18de92e2d0da2c</t>
+          <t>https://www.indeed.com/viewjob?jk=ad7533e66ad7d7d8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>Senior Developer I - Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
+          <t>AWS, Azure, Spark, Scala, Kafka, Polars, Snowflake, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d784ad2795e0379d</t>
+          <t>https://www.indeed.com/viewjob?jk=b4e3803b26dd25a2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Full Stack Software Engineer, Security &amp; Information Technology - USDS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tunnl</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, RDS, Scala, DynamoDB, Splunk</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b66532c29a2d2fb3</t>
+          <t>https://www.indeed.com/viewjob?jk=b8131bdacb963c45</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Information Technology - BI Developer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TCC Verizon Authorized Retailer</t>
+          <t>ICAT Logistics, Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Fishers, IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad7533e66ad7d7d8</t>
+          <t>https://www.indeed.com/viewjob?jk=490396287ca9423d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Developer I - Data Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, Kafka, Polars, Snowflake, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4e3803b26dd25a2</t>
+          <t>https://www.indeed.com/viewjob?jk=eba11dc550c0d956</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer, Security &amp; Information Technology - USDS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8131bdacb963c45</t>
+          <t>https://www.indeed.com/viewjob?jk=eea1d0eeb00ba384</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Python Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ICAT Logistics, Inc.</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, Azure, GCP, Hadoop, HDFS, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=490396287ca9423d</t>
+          <t>https://www.indeed.com/viewjob?jk=da84632d9568dfce</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eba11dc550c0d956</t>
+          <t>https://www.indeed.com/viewjob?jk=336bfe0af38918a1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>SIGNITIVES</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
+          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eea1d0eeb00ba384</t>
+          <t>https://www.indeed.com/viewjob?jk=afef76c3c4cb302e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Anteriad</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Google Cloud Platform, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=336bfe0af38918a1</t>
+          <t>https://www.indeed.com/viewjob?jk=5a53981dcd494255</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Sr. Software Engineer II (DevOps)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SIGNITIVES</t>
+          <t>Hi Marley</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, DynamoDB, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afef76c3c4cb302e</t>
+          <t>https://www.indeed.com/viewjob?jk=57e6ba06d3a7b30f</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Anteriad</t>
+          <t>Applied Information Sciences</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Google Cloud Platform, Dataflow, Cloud Storage, Spark</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a53981dcd494255</t>
+          <t>https://www.indeed.com/viewjob?jk=0b4d756dafb24330</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II (DevOps)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hi Marley</t>
+          <t>Bambee</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, DynamoDB, ETL, ELT</t>
+          <t>Redshift, ECS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57e6ba06d3a7b30f</t>
+          <t>https://www.indeed.com/viewjob?jk=3e3ad167874c8532</t>
         </is>
       </c>
     </row>
@@ -1313,20 +1313,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Applied Information Sciences</t>
+          <t>ICAT Logistics, Inc.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Lake Storage, GCP, BigQuery, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,59 +1336,59 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b4d756dafb24330</t>
+          <t>https://www.indeed.com/viewjob?jk=7dfde2e65a7bc1cc</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Fabric Data Engineer</t>
+          <t>Data Engineer - Data Services</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lasting Change Inc</t>
+          <t>Crown Equipment</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>New Bremen, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3a86d1b4b4bd7e7</t>
+          <t>https://www.indeed.com/viewjob?jk=426a2df1dcd32427</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Services</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Crown Equipment</t>
+          <t>Rediantt</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New Bremen, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=426a2df1dcd32427</t>
+          <t>https://www.indeed.com/viewjob?jk=60d3683730583b9c</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer, Data Engineering and Analytics - USDS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Amphenol</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Nashua, NH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, S3, RDS, Hadoop, HDFS, Hive, Flume, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70728c10caf53950</t>
+          <t>https://www.indeed.com/viewjob?jk=5b155ae7711afa6e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Engineering and Analytics - USDS</t>
+          <t>AI Engineering Intern</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Harvard Services Group, Inc</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Hadoop, HDFS, Hive, Flume, Spark, Scala, Kafka</t>
+          <t>Redshift, ECS, RDS, BigQuery, Snowflake, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b155ae7711afa6e</t>
+          <t>https://www.indeed.com/viewjob?jk=9a6b9d95984b1f2d</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Harvard Services Group, Inc</t>
+          <t>Harvard Maintenance, Inc.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a6b9d95984b1f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=780346cd358075a8</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI Engineering Intern</t>
+          <t>Senior Site Reliability Engineer (contract)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Harvard Maintenance, Inc.</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Redshift, ECS, RDS, BigQuery, Snowflake, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Kafka, Oracle, MongoDB, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,94 +1721,94 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780346cd358075a8</t>
+          <t>https://www.indeed.com/viewjob?jk=26d05b8ec42e7cf9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (contract)</t>
+          <t>Senior Cloud Software Engineer - Database</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>TP-LINK</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Kafka, Oracle, MongoDB, Splunk, Jenkins</t>
+          <t>AWS, IAM, RDS, Cloud Storage, Scala, Kafka, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26d05b8ec42e7cf9</t>
+          <t>https://www.indeed.com/viewjob?jk=c97fb5b4fe767905</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Airvoyant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TRAX USA Corp.</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, MySQL</t>
+          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1046b4cc869c21</t>
+          <t>https://www.indeed.com/viewjob?jk=424fe727a6834d5b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Event Hubs, Snowflake, PostgreSQL, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424fe727a6834d5b</t>
+          <t>https://www.indeed.com/viewjob?jk=a5cff3964beedb24</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Engineer</t>
+          <t>Senior Software Engineer, ML Platform | Parafin</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>carnaby fox</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Event Hubs, Snowflake, PostgreSQL, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Kinesis, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5cff3964beedb24</t>
+          <t>https://www.indeed.com/viewjob?jk=4377663fa2ea1245</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, ML Platform | Parafin</t>
+          <t>Data Engineer - III</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>carnaby fox</t>
+          <t>Noise Consulting Group</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, MLOps</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4377663fa2ea1245</t>
+          <t>https://www.indeed.com/viewjob?jk=2baa480224d46766</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer - III</t>
+          <t>Data Engineer, Data Engineering and Analytics - USDS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Noise Consulting Group</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, RDS, Hadoop, HDFS, Hive, Flume, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2baa480224d46766</t>
+          <t>https://www.indeed.com/viewjob?jk=d72ef2291619fe5e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AmaWaterways</t>
+          <t>Artisan Studios, LLC DBA Amy Howard At Home &amp; A Makers' Studio</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Asheville, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, S3, IAM, RDS, Spark, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c980ae96d7c71b5b</t>
+          <t>https://www.indeed.com/viewjob?jk=7350027af6d67644</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Engineering and Analytics - USDS</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Verification Technologies LLC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Henderson, NV, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Hadoop, HDFS, Hive, Flume, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, Athena, Timestream, Step Functions, S3, SQS, API Gateway, IAM, RDS</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72ef2291619fe5e</t>
+          <t>https://www.indeed.com/viewjob?jk=97a02535a97e1c4c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Senior BI Analyst</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Artisan Studios, LLC DBA Amy Howard At Home &amp; A Makers' Studio</t>
+          <t>Walker &amp; Dunlop</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Asheville, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, IAM, RDS, Spark, MLOps, CI/CD</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7350027af6d67644</t>
+          <t>https://www.indeed.com/viewjob?jk=827ebbc8cea913b8</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Verification Technologies LLC</t>
+          <t>Point Wild</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Henderson, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, Timestream, Step Functions, S3, SQS, API Gateway, IAM, RDS</t>
+          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,19 +2071,19 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97a02535a97e1c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2022ce8366d457</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior BI Analyst</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Walker &amp; Dunlop</t>
+          <t>Point Wild</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=827ebbc8cea913b8</t>
+          <t>https://www.indeed.com/viewjob?jk=71457be51c270627</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer, Data &amp; AI Infrastructure</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>McKinney</t>
+          <t>Point Wild</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, Scala, MongoDB, ELT, CI/CD</t>
+          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fad3b7a6b278561a</t>
+          <t>https://www.indeed.com/viewjob?jk=ccc6509aa3c8ec42</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Analytical Engineer, Payment Data Intelligence - USDS</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Point Wild</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a567c2b339c20c2f</t>
+          <t>https://www.indeed.com/viewjob?jk=d8f514785edf8fdc</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Azure Databricks Platform Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Point Wild</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Event Hubs, Medallion Architecture, Spark, PySpark, SQL Server, Data Modeling</t>
+          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=809ad06a2b50c327</t>
+          <t>https://www.indeed.com/viewjob?jk=7f99d76959b32539</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Development Engineer â€“ Backend / Platform</t>
+          <t>Data Analytical Engineer, Payment Data Intelligence - USDS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Sinclair Broadcast Group</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41a635808e4af271</t>
+          <t>https://www.indeed.com/viewjob?jk=a567c2b339c20c2f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Site Reliability Engineer</t>
+          <t>Azure Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Event Hubs, Medallion Architecture, Spark, PySpark, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e4b910ec252456f</t>
+          <t>https://www.indeed.com/viewjob?jk=809ad06a2b50c327</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS</t>
+          <t>AI ML Data Scientist</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Westlake Village, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, ELT, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>Azure, Hadoop, YARN, Spark, PySpark, Kafka, Oracle, NoSQL, Tableau, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bce752ad6855e523</t>
+          <t>https://www.indeed.com/viewjob?jk=ce609bae5ee0d5a2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DevX / Developer Operations (Partner 16, Partner 18), ASG</t>
+          <t>Software Development Engineer â€“ Backend / Platform</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>a16z</t>
+          <t>Sinclair Broadcast Group</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>Kinesis, IAM, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0f26d4983647c6b</t>
+          <t>https://www.indeed.com/viewjob?jk=41a635808e4af271</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>Software Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Vytl Controls Group</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f97f2d7c736b559</t>
+          <t>https://www.indeed.com/viewjob?jk=8e4b910ec252456f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Informatica ETL Developer - 6326296</t>
+          <t>Software Engineering SMTS</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, Git</t>
+          <t>AWS, RDS, Scala, ELT, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1a17c04578e9be3</t>
+          <t>https://www.indeed.com/viewjob?jk=bce752ad6855e523</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Informatica ETL Developer - 6326296</t>
+          <t>DevX / Developer Operations (Partner 16, Partner 18), ASG</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Andreessen Horowitz</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,59 +2456,59 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21eab84e17f0b1ac</t>
+          <t>https://www.indeed.com/viewjob?jk=2570942407162c4a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer III</t>
+          <t>DevX / Developer Operations (Partner 16, Partner 18), ASG</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>a16z</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, MLflow, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b58a2b9f1b9c3a51</t>
+          <t>https://www.indeed.com/viewjob?jk=e0f26d4983647c6b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Informatica ETL Developer - 6326296</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Vytl Controls Group</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, Git</t>
+          <t>RDS, Azure, Databricks, Scala, SQL Server, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40516db2dcf106b5</t>
+          <t>https://www.indeed.com/viewjob?jk=2f97f2d7c736b559</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Informatica ETL Developer - 6326296</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564f104de61b3f0a</t>
+          <t>https://www.indeed.com/viewjob?jk=e1a17c04578e9be3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Privacy &amp; Infrastructure - USDS</t>
+          <t>Informatica ETL Developer - 6326296</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, HDFS, Hive, Spark, Kafka, MySQL, NoSQL, Kubernetes</t>
+          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=625f5552fcee590f</t>
+          <t>https://www.indeed.com/viewjob?jk=21eab84e17f0b1ac</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Machine Learning Engineer III</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, SQS, API Gateway, ECS, RDS, Jenkins</t>
+          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, MLflow, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e888182752c6207b</t>
+          <t>https://www.indeed.com/viewjob?jk=b58a2b9f1b9c3a51</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ERP SAVVY LLC</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Skillman, NJ, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Oozie, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a04b59dd3c9c139</t>
+          <t>https://www.indeed.com/viewjob?jk=564f104de61b3f0a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer, Data Privacy &amp; Infrastructure - USDS</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, IAM, RDS, HDFS, Hive, Spark, Kafka, MySQL, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=936e44ddac734d7b</t>
+          <t>https://www.indeed.com/viewjob?jk=625f5552fcee590f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer, Application Development</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, SQS, API Gateway, ECS, RDS, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e58bc4277f70431</t>
+          <t>https://www.indeed.com/viewjob?jk=e888182752c6207b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer, Application Development</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ERP SAVVY LLC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Skillman, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>Hadoop, HDFS, Oozie, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fea29a3880a03255</t>
+          <t>https://www.indeed.com/viewjob?jk=8a04b59dd3c9c139</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer, Application Development</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb3cb19cae9db9b</t>
+          <t>https://www.indeed.com/viewjob?jk=936e44ddac734d7b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Intelligence Solutions Architect</t>
+          <t>Full Stack Senior Engineer, Application Development</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Q2ebanking</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a34770e6525c28d7</t>
+          <t>https://www.indeed.com/viewjob?jk=4e58bc4277f70431</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Senior Engineer, Application Development</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Safelease</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6884b300f1b32ae4</t>
+          <t>https://www.indeed.com/viewjob?jk=fea29a3880a03255</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Senior Engineer, Application Development</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1849a5b7a2f2af9b</t>
+          <t>https://www.indeed.com/viewjob?jk=3bb3cb19cae9db9b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Sr. Full Stack Engineer - AI Forward Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Arbitration Forums Inc.</t>
+          <t>CarParts.com</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Power BI, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=213170f837efaaa7</t>
+          <t>https://www.indeed.com/viewjob?jk=81e7e89cef9a97da</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Java Developer (Connected Services)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69b02ec8d04b37bb</t>
+          <t>https://www.indeed.com/viewjob?jk=fa3dcc861e4ac768</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer Fish Data Systems</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PACIFIC STATES MARINE FISHERIES COMMISSION</t>
+          <t>Safelease</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Oracle, SQL Server, PostgreSQL, ELT, Power BI, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b90c3fac511dfb2</t>
+          <t>https://www.indeed.com/viewjob?jk=6884b300f1b32ae4</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Full Stack Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>The Akanksha LLC</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Medallion Architecture, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaf16acc114cd913</t>
+          <t>https://www.indeed.com/viewjob?jk=1849a5b7a2f2af9b</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Scientific System of Record</t>
+          <t>Full Stack Software Engineer Fish Data Systems</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>PACIFIC STATES MARINE FISHERIES COMMISSION</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Data Factory, Oracle, SQL Server, PostgreSQL, ELT, Power BI, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a083efe79b22465</t>
+          <t>https://www.indeed.com/viewjob?jk=0b90c3fac511dfb2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Scientific System of Record</t>
+          <t>Full Stack Cloud Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>The Akanksha LLC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, API Gateway, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=233d27bbc07fd70f</t>
+          <t>https://www.indeed.com/viewjob?jk=aaf16acc114cd913</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Senior Software Engineer, Scientific System of Record</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=226e96da47ff2b1a</t>
+          <t>https://www.indeed.com/viewjob?jk=0a083efe79b22465</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Consultant – Data Engineer &amp; Governance</t>
+          <t>Senior Software Engineer, Scientific System of Record</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Quisitive</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd77d29cb01573c</t>
+          <t>https://www.indeed.com/viewjob?jk=233d27bbc07fd70f</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer â€“ Python/AI</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb44a4b768419ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=226e96da47ff2b1a</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Oracle)</t>
+          <t>Senior Data Consultant – Data Engineer &amp; Governance</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>Quisitive</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b698f84637b7e148</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd77d29cb01573c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Data Engineer â€“ Python/AI</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Zookeeper, Scala, Kafka, Oracle, CI/CD</t>
+          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d5b2e7bc490d9bd</t>
+          <t>https://www.indeed.com/viewjob?jk=bb44a4b768419ca2</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Oracle)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>Bitscopic</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Azure, Medallion Architecture, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8d59fd93890be9a</t>
+          <t>https://www.indeed.com/viewjob?jk=b698f84637b7e148</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer - Analytics</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EvergreenHealth</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, Star Schema, ETL, Power BI, Tableau, Azure DevOps, Git</t>
+          <t>Redshift, Databricks, BigQuery, Spark, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=847c2fe533f1ec86</t>
+          <t>https://www.indeed.com/viewjob?jk=f16a0fa5da61102a</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (React/Typescript)</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Vertafore</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Zookeeper, Scala, Kafka, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=757afec97d5d27e0</t>
+          <t>https://www.indeed.com/viewjob?jk=3d5b2e7bc490d9bd</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AI LLM Engineer</t>
+          <t>Senior Machine Learning Engineer, Model Risk Management</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Siemens Healthineers</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, Data Modeling, ELT, Power BI, Git, Python</t>
+          <t>AWS, RDS, Databricks, GCP, Vertex AI, Snowflake, ETL, MLflow, pytest, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77cc10c4736bb6e5</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4b8c7a56e0e088</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Lakebase Sales Specialist- Financial Services</t>
+          <t>SAS Developer (with Admin Background)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d86224c98360290</t>
+          <t>https://www.indeed.com/viewjob?jk=f708bb2089c8e37e</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>SAS Developer (with Admin Background)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Spark, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a874d216618930</t>
+          <t>https://www.indeed.com/viewjob?jk=2b030dd9a627fd2c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AI Software Engineer - Center for Diagnostics and Artificial Intelligence</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Cleveland Clinic</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, CI/CD, Docker</t>
+          <t>Azure, Medallion Architecture, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10aaff122c10f274</t>
+          <t>https://www.indeed.com/viewjob?jk=e8d59fd93890be9a</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr AI Platform Engineer</t>
+          <t>Business Intelligence Developer - Analytics</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>EvergreenHealth</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Scala, Data Modeling, Star Schema, ETL, Power BI, Tableau, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f8d87a308d60fa</t>
+          <t>https://www.indeed.com/viewjob?jk=847c2fe533f1ec86</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer - Java - Loops</t>
+          <t>Sr. Software Engineer (React/Typescript)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Copperleaf Technologies Inc.</t>
+          <t>Vertafore</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Git, Datadog</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe4ff78e6fcedc19</t>
+          <t>https://www.indeed.com/viewjob?jk=757afec97d5d27e0</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI LLM Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Siemens Healthineers</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Splunk, CI/CD, Kubernetes, Git</t>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, Data Modeling, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d604ebca572d9a0d</t>
+          <t>https://www.indeed.com/viewjob?jk=77cc10c4736bb6e5</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Lakebase Sales Specialist- Financial Services</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Splunk, CI/CD, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=244f96a693bca9f8</t>
+          <t>https://www.indeed.com/viewjob?jk=6d86224c98360290</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,15 +3706,190 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
+          <t>Redshift, Databricks, BigQuery, Spark, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90a874d216618930</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>AI Software Engineer - Center for Diagnostics and Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Cleveland Clinic</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>S3, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=10aaff122c10f274</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Data Engineer - Java - Loops</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Copperleaf Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe4ff78e6fcedc19</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
           <t>RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Splunk, CI/CD, Kubernetes, Git</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d604ebca572d9a0d</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>West Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Splunk, CI/CD, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=244f96a693bca9f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Splunk, CI/CD, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4229f7f9f0a4e0f7</t>
         </is>

--- a/results/job_matches_2026-06-04.xlsx
+++ b/results/job_matches_2026-06-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1308,122 +1308,122 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>E T Consultant</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ICAT Logistics, Inc.</t>
+          <t>World Bank Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Lake Storage, GCP, BigQuery, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dfde2e65a7bc1cc</t>
+          <t>https://www.indeed.com/viewjob?jk=3d019be2ca0c38b6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Services</t>
+          <t>Senior Systems Administrator</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Crown Equipment</t>
+          <t>Anduril</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New Bremen, OH, US USA</t>
+          <t>Ashville, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=426a2df1dcd32427</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c796f5ba5948fe</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Modem Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Rediantt</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d3683730583b9c</t>
+          <t>https://www.indeed.com/viewjob?jk=63cf613962496b27</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Associate Data Engineer (REMOTE)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>ICAT Logistics, Inc.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Data Lake Storage, GCP, BigQuery, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f62c64972906caa0</t>
+          <t>https://www.indeed.com/viewjob?jk=7dfde2e65a7bc1cc</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Associate Data Engineer (REMOTE)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, dbt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad092c66101d7698</t>
+          <t>https://www.indeed.com/viewjob?jk=60aa962ac2f33982</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Cloud &amp; AI Platform [On-Site]</t>
+          <t>Data Engineer - Data Services</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Crown Equipment</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>New Bremen, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7ba4a006c4d066d</t>
+          <t>https://www.indeed.com/viewjob?jk=426a2df1dcd32427</t>
         </is>
       </c>
     </row>
@@ -1523,12 +1523,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Rediantt</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7433f9b8b5c4a5a6</t>
+          <t>https://www.indeed.com/viewjob?jk=60d3683730583b9c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Data Engineer (REMOTE)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddf7449abdd32b05</t>
+          <t>https://www.indeed.com/viewjob?jk=f62c64972906caa0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Engineering and Analytics - USDS</t>
+          <t>Associate Data Engineer (REMOTE)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Hadoop, HDFS, Hive, Flume, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b155ae7711afa6e</t>
+          <t>https://www.indeed.com/viewjob?jk=ad092c66101d7698</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI Engineering Intern</t>
+          <t>Sr. Data Engineer - Cloud &amp; AI Platform [On-Site]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Harvard Services Group, Inc</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Redshift, ECS, RDS, BigQuery, Snowflake, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
+          <t>AWS, Glue, EMR, RDS, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a6b9d95984b1f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=f7ba4a006c4d066d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI Engineering Intern</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Harvard Maintenance, Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Redshift, ECS, RDS, BigQuery, Snowflake, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780346cd358075a8</t>
+          <t>https://www.indeed.com/viewjob?jk=7433f9b8b5c4a5a6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (contract)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Kafka, Oracle, MongoDB, Splunk, Jenkins</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26d05b8ec42e7cf9</t>
+          <t>https://www.indeed.com/viewjob?jk=ddf7449abdd32b05</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer - Database</t>
+          <t>Data Engineer, Data Engineering and Analytics - USDS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TP-LINK</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Cloud Storage, Scala, Kafka, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Hadoop, HDFS, Hive, Flume, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c97fb5b4fe767905</t>
+          <t>https://www.indeed.com/viewjob?jk=5b155ae7711afa6e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineering Intern</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>Harvard Services Group, Inc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
+          <t>Redshift, ECS, RDS, BigQuery, Snowflake, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424fe727a6834d5b</t>
+          <t>https://www.indeed.com/viewjob?jk=9a6b9d95984b1f2d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Engineer</t>
+          <t>AI Engineering Intern</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Harvard Maintenance, Inc.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Event Hubs, Snowflake, PostgreSQL, Dimensional Modeling, Snowflake Schema</t>
+          <t>Redshift, ECS, RDS, BigQuery, Snowflake, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5cff3964beedb24</t>
+          <t>https://www.indeed.com/viewjob?jk=780346cd358075a8</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, ML Platform | Parafin</t>
+          <t>Senior Site Reliability Engineer (contract)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>carnaby fox</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, MLOps</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Kafka, Oracle, MongoDB, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4377663fa2ea1245</t>
+          <t>https://www.indeed.com/viewjob?jk=26d05b8ec42e7cf9</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer - III</t>
+          <t>Senior Cloud Software Engineer - Database</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Noise Consulting Group</t>
+          <t>TP-LINK</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, RDS, Cloud Storage, Scala, Kafka, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2baa480224d46766</t>
+          <t>https://www.indeed.com/viewjob?jk=c97fb5b4fe767905</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Engineering and Analytics - USDS</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Hadoop, HDFS, Hive, Flume, Spark, Scala, Kafka</t>
+          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72ef2291619fe5e</t>
+          <t>https://www.indeed.com/viewjob?jk=424fe727a6834d5b</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Senior Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Artisan Studios, LLC DBA Amy Howard At Home &amp; A Makers' Studio</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Asheville, NC, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, IAM, RDS, Spark, MLOps, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Event Hubs, Snowflake, PostgreSQL, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7350027af6d67644</t>
+          <t>https://www.indeed.com/viewjob?jk=a5cff3964beedb24</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior Software Engineer, ML Platform | Parafin</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Verification Technologies LLC</t>
+          <t>carnaby fox</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Henderson, NV, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, Timestream, Step Functions, S3, SQS, API Gateway, IAM, RDS</t>
+          <t>AWS, Kinesis, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97a02535a97e1c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=4377663fa2ea1245</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior BI Analyst</t>
+          <t>Data Engineer - III</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Walker &amp; Dunlop</t>
+          <t>Noise Consulting Group</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=827ebbc8cea913b8</t>
+          <t>https://www.indeed.com/viewjob?jk=2baa480224d46766</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer, Data Engineering and Analytics - USDS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Point Wild</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, S3, RDS, Hadoop, HDFS, Hive, Flume, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e2022ce8366d457</t>
+          <t>https://www.indeed.com/viewjob?jk=d72ef2291619fe5e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer - Full Stack Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Point Wild</t>
+          <t>Benda Infotech</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71457be51c270627</t>
+          <t>https://www.indeed.com/viewjob?jk=c284602b40afa505</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Point Wild</t>
+          <t>Verification Technologies LLC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Henderson, NV, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, Lambda, Athena, Timestream, Step Functions, S3, SQS, API Gateway, IAM, RDS</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,19 +2141,19 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccc6509aa3c8ec42</t>
+          <t>https://www.indeed.com/viewjob?jk=97a02535a97e1c4c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior BI Analyst</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Point Wild</t>
+          <t>Walker &amp; Dunlop</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8f514785edf8fdc</t>
+          <t>https://www.indeed.com/viewjob?jk=827ebbc8cea913b8</t>
         </is>
       </c>
     </row>
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f99d76959b32539</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2022ce8366d457</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Analytical Engineer, Payment Data Intelligence - USDS</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Point Wild</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a567c2b339c20c2f</t>
+          <t>https://www.indeed.com/viewjob?jk=71457be51c270627</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Azure Databricks Platform Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Point Wild</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Event Hubs, Medallion Architecture, Spark, PySpark, SQL Server, Data Modeling</t>
+          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=809ad06a2b50c327</t>
+          <t>https://www.indeed.com/viewjob?jk=ccc6509aa3c8ec42</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AI ML Data Scientist</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Point Wild</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Westlake Village, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Azure, Hadoop, YARN, Spark, PySpark, Kafka, Oracle, NoSQL, Tableau, Docker</t>
+          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce609bae5ee0d5a2</t>
+          <t>https://www.indeed.com/viewjob?jk=d8f514785edf8fdc</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Development Engineer â€“ Backend / Platform</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Sinclair Broadcast Group</t>
+          <t>Point Wild</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41a635808e4af271</t>
+          <t>https://www.indeed.com/viewjob?jk=7f99d76959b32539</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Site Reliability Engineer</t>
+          <t>Data Analytical Engineer, Payment Data Intelligence - USDS</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e4b910ec252456f</t>
+          <t>https://www.indeed.com/viewjob?jk=a567c2b339c20c2f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS</t>
+          <t>Azure Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, ELT, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Event Hubs, Medallion Architecture, Spark, PySpark, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bce752ad6855e523</t>
+          <t>https://www.indeed.com/viewjob?jk=809ad06a2b50c327</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DevX / Developer Operations (Partner 16, Partner 18), ASG</t>
+          <t>AI ML Data Scientist</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Andreessen Horowitz</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Westlake Village, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>Azure, Hadoop, YARN, Spark, PySpark, Kafka, Oracle, NoSQL, Tableau, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2570942407162c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=ce609bae5ee0d5a2</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DevX / Developer Operations (Partner 16, Partner 18), ASG</t>
+          <t>Software Development Engineer â€“ Backend / Platform</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>a16z</t>
+          <t>Sinclair Broadcast Group</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>Kinesis, IAM, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0f26d4983647c6b</t>
+          <t>https://www.indeed.com/viewjob?jk=41a635808e4af271</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>Software Engineering SMTS</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Vytl Controls Group</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Scala, ELT, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f97f2d7c736b559</t>
+          <t>https://www.indeed.com/viewjob?jk=bce752ad6855e523</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Informatica ETL Developer - 6326296</t>
+          <t>DevX / Developer Operations (Partner 16, Partner 18), ASG</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Andreessen Horowitz</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1a17c04578e9be3</t>
+          <t>https://www.indeed.com/viewjob?jk=2570942407162c4a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Informatica ETL Developer - 6326296</t>
+          <t>Software Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, Git</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,59 +2596,59 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21eab84e17f0b1ac</t>
+          <t>https://www.indeed.com/viewjob?jk=8e4b910ec252456f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer III</t>
+          <t>DevX / Developer Operations (Partner 16, Partner 18), ASG</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>a16z</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, MLflow, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b58a2b9f1b9c3a51</t>
+          <t>https://www.indeed.com/viewjob?jk=e0f26d4983647c6b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Vytl Controls Group</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, SQL Server, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564f104de61b3f0a</t>
+          <t>https://www.indeed.com/viewjob?jk=2f97f2d7c736b559</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Privacy &amp; Infrastructure - USDS</t>
+          <t>Informatica ETL Developer - 6326296</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, HDFS, Hive, Spark, Kafka, MySQL, NoSQL, Kubernetes</t>
+          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=625f5552fcee590f</t>
+          <t>https://www.indeed.com/viewjob?jk=e1a17c04578e9be3</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Informatica ETL Developer - 6326296</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, SQS, API Gateway, ECS, RDS, Jenkins</t>
+          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e888182752c6207b</t>
+          <t>https://www.indeed.com/viewjob?jk=21eab84e17f0b1ac</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Machine Learning Engineer III</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ERP SAVVY LLC</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Skillman, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Oozie, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, MLflow, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a04b59dd3c9c139</t>
+          <t>https://www.indeed.com/viewjob?jk=b58a2b9f1b9c3a51</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer, Data Privacy &amp; Infrastructure - USDS</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, IAM, RDS, HDFS, Hive, Spark, Kafka, MySQL, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=936e44ddac734d7b</t>
+          <t>https://www.indeed.com/viewjob?jk=625f5552fcee590f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer, Application Development</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, SQS, API Gateway, ECS, RDS, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e58bc4277f70431</t>
+          <t>https://www.indeed.com/viewjob?jk=e888182752c6207b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer, Application Development</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ERP SAVVY LLC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Skillman, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>Hadoop, HDFS, Oozie, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fea29a3880a03255</t>
+          <t>https://www.indeed.com/viewjob?jk=8a04b59dd3c9c139</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer, Application Development</t>
+          <t>Resident Solutions Architect - Digital Native Business</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb3cb19cae9db9b</t>
+          <t>https://www.indeed.com/viewjob?jk=dec276bec6c38a67</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer - AI Forward Engineer</t>
+          <t>Resident Solutions Architect - Digital Native Business</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CarParts.com</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81e7e89cef9a97da</t>
+          <t>https://www.indeed.com/viewjob?jk=377873b4a91a42db</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Java Developer (Connected Services)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa3dcc861e4ac768</t>
+          <t>https://www.indeed.com/viewjob?jk=936e44ddac734d7b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Full Stack Engineer - AI Forward Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Safelease</t>
+          <t>CarParts.com</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,17 +3006,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6884b300f1b32ae4</t>
+          <t>https://www.indeed.com/viewjob?jk=81e7e89cef9a97da</t>
         </is>
       </c>
     </row>
@@ -3028,12 +3028,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Safelease</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1849a5b7a2f2af9b</t>
+          <t>https://www.indeed.com/viewjob?jk=6884b300f1b32ae4</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer Fish Data Systems</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PACIFIC STATES MARINE FISHERIES COMMISSION</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Oracle, SQL Server, PostgreSQL, ELT, Power BI, CI/CD, Docker</t>
+          <t>RDS, Azure, Medallion Architecture, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b90c3fac511dfb2</t>
+          <t>https://www.indeed.com/viewjob?jk=1849a5b7a2f2af9b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Full Stack Cloud Engineer</t>
+          <t>Java Developer (Connected Services)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>The Akanksha LLC</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaf16acc114cd913</t>
+          <t>https://www.indeed.com/viewjob?jk=fa3dcc861e4ac768</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Scientific System of Record</t>
+          <t>Full Stack Senior Engineer, Application Development</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a083efe79b22465</t>
+          <t>https://www.indeed.com/viewjob?jk=4e58bc4277f70431</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Scientific System of Record</t>
+          <t>Full Stack Senior Engineer, Application Development</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=233d27bbc07fd70f</t>
+          <t>https://www.indeed.com/viewjob?jk=fea29a3880a03255</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Full Stack Senior Engineer, Application Development</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=226e96da47ff2b1a</t>
+          <t>https://www.indeed.com/viewjob?jk=3bb3cb19cae9db9b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Consultant – Data Engineer &amp; Governance</t>
+          <t>Full Stack Software Engineer Fish Data Systems</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Quisitive</t>
+          <t>PACIFIC STATES MARINE FISHERIES COMMISSION</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Data Factory, Oracle, SQL Server, PostgreSQL, ELT, Power BI, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd77d29cb01573c</t>
+          <t>https://www.indeed.com/viewjob?jk=0b90c3fac511dfb2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer â€“ Python/AI</t>
+          <t>Full Stack Cloud Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>The Akanksha LLC</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
+          <t>AWS, Lambda, API Gateway, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb44a4b768419ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=aaf16acc114cd913</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Oracle)</t>
+          <t>Senior Software Engineer, Scientific System of Record</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,59 +3331,59 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b698f84637b7e148</t>
+          <t>https://www.indeed.com/viewjob?jk=0a083efe79b22465</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Software Engineer, Scientific System of Record</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Spark, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f16a0fa5da61102a</t>
+          <t>https://www.indeed.com/viewjob?jk=233d27bbc07fd70f</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Data Consultant – Data Engineer &amp; GovernanceNew</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Quisitive</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Zookeeper, Scala, Kafka, Oracle, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d5b2e7bc490d9bd</t>
+          <t>https://www.indeed.com/viewjob?jk=69dc7b2b5de56422</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Model Risk Management</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Vertex AI, Snowflake, ETL, MLflow, pytest, Git</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4b8c7a56e0e088</t>
+          <t>https://www.indeed.com/viewjob?jk=226e96da47ff2b1a</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SAS Developer (with Admin Background)</t>
+          <t>Senior Data Consultant – Data Engineer &amp; Governance</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Quisitive</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, ETL, CI/CD, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f708bb2089c8e37e</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd77d29cb01573c</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SAS Developer (with Admin Background)</t>
+          <t>Data Engineer â€“ Python/AI</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, ETL, CI/CD, Git</t>
+          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b030dd9a627fd2c</t>
+          <t>https://www.indeed.com/viewjob?jk=bb44a4b768419ca2</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - Finance Modernization</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Azure, Medallion Architecture, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Spark, Scala, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8d59fd93890be9a</t>
+          <t>https://www.indeed.com/viewjob?jk=15ee917ec6e025e8</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer - Analytics</t>
+          <t>Salesforce Technical Architect, Data &amp; AI</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>EvergreenHealth</t>
+          <t>NeuraFlash, Part of Accenture</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, Star Schema, ETL, Power BI, Tableau, Azure DevOps, Git</t>
+          <t>AWS, Redshift, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=847c2fe533f1ec86</t>
+          <t>https://www.indeed.com/viewjob?jk=3420dddc661e222d</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (React/Typescript)</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Vertafore</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Zookeeper, Scala, Kafka, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=757afec97d5d27e0</t>
+          <t>https://www.indeed.com/viewjob?jk=3d5b2e7bc490d9bd</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AI LLM Engineer</t>
+          <t>Senior Machine Learning Engineer, Model Risk Management</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Siemens Healthineers</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, Data Modeling, ELT, Power BI, Git, Python</t>
+          <t>AWS, RDS, Databricks, GCP, Vertex AI, Snowflake, ETL, MLflow, pytest, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77cc10c4736bb6e5</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4b8c7a56e0e088</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Lakebase Sales Specialist- Financial Services</t>
+          <t>AI LLM Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Siemens Healthineers</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, Data Modeling, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d86224c98360290</t>
+          <t>https://www.indeed.com/viewjob?jk=77cc10c4736bb6e5</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Lakebase Sales Specialist- Financial Services</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Spark, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a874d216618930</t>
+          <t>https://www.indeed.com/viewjob?jk=6d86224c98360290</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AI Software Engineer - Center for Diagnostics and Artificial Intelligence</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Cleveland Clinic</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, CI/CD, Docker</t>
+          <t>Redshift, Databricks, BigQuery, Spark, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10aaff122c10f274</t>
+          <t>https://www.indeed.com/viewjob?jk=90a874d216618930</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer - Java - Loops</t>
+          <t>AI Software Engineer - Center for Diagnostics and Artificial Intelligence</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Copperleaf Technologies Inc.</t>
+          <t>Cleveland Clinic</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Git, Datadog</t>
+          <t>S3, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe4ff78e6fcedc19</t>
+          <t>https://www.indeed.com/viewjob?jk=10aaff122c10f274</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>SAS Developer (with Admin Background)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Splunk, CI/CD, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d604ebca572d9a0d</t>
+          <t>https://www.indeed.com/viewjob?jk=f708bb2089c8e37e</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>SAS Developer (with Admin Background)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Splunk, CI/CD, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=244f96a693bca9f8</t>
+          <t>https://www.indeed.com/viewjob?jk=2b030dd9a627fd2c</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,15 +3881,225 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
+          <t>Azure, Medallion Architecture, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e8d59fd93890be9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Business Intelligence Developer - Analytics</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>EvergreenHealth</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Kirkland, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Data Modeling, Star Schema, ETL, Power BI, Tableau, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=847c2fe533f1ec86</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer (React/Typescript)</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Vertafore</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=757afec97d5d27e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Data Engineer - Java - Loops</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Copperleaf Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe4ff78e6fcedc19</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
           <t>RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Splunk, CI/CD, Kubernetes, Git</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d604ebca572d9a0d</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>West Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Splunk, CI/CD, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=244f96a693bca9f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Splunk, CI/CD, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4229f7f9f0a4e0f7</t>
         </is>

--- a/results/job_matches_2026-06-04.xlsx
+++ b/results/job_matches_2026-06-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Information Technology - BI Developer</t>
+          <t>Senior ETL Developer (Azure &amp; MDM/Reltio Focus)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TCC Verizon Authorized Retailer</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fishers, IN, US USA</t>
+          <t>Duncan, SC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,42 +871,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad7533e66ad7d7d8</t>
+          <t>https://www.indeed.com/viewjob?jk=6bde84b2e0c4d7b5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Developer I - Data Engineer</t>
+          <t>Information Technology - BI Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>TCC Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fishers, IN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, Kafka, Polars, Snowflake, Star Schema, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4e3803b26dd25a2</t>
+          <t>https://www.indeed.com/viewjob?jk=ad7533e66ad7d7d8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer, Security &amp; Information Technology - USDS</t>
+          <t>Senior Developer I - Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Azure, Spark, Scala, Kafka, Polars, Snowflake, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8131bdacb963c45</t>
+          <t>https://www.indeed.com/viewjob?jk=b4e3803b26dd25a2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Full Stack Software Engineer, Security &amp; Information Technology - USDS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ICAT Logistics, Inc.</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=490396287ca9423d</t>
+          <t>https://www.indeed.com/viewjob?jk=b8131bdacb963c45</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior Automation Platform Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, AWS CodePipeline, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eba11dc550c0d956</t>
+          <t>https://www.indeed.com/viewjob?jk=bc94922007c35c18</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>ICAT Logistics, Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eea1d0eeb00ba384</t>
+          <t>https://www.indeed.com/viewjob?jk=490396287ca9423d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Python Data Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Hadoop, HDFS, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da84632d9568dfce</t>
+          <t>https://www.indeed.com/viewjob?jk=eba11dc550c0d956</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,59 +1126,59 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=336bfe0af38918a1</t>
+          <t>https://www.indeed.com/viewjob?jk=eea1d0eeb00ba384</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Python Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SIGNITIVES</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, S3, Azure, GCP, Hadoop, HDFS, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afef76c3c4cb302e</t>
+          <t>https://www.indeed.com/viewjob?jk=da84632d9568dfce</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Anteriad</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Google Cloud Platform, Dataflow, Cloud Storage, Spark</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a53981dcd494255</t>
+          <t>https://www.indeed.com/viewjob?jk=336bfe0af38918a1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II (DevOps)</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hi Marley</t>
+          <t>SIGNITIVES</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, DynamoDB, ETL, ELT</t>
+          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57e6ba06d3a7b30f</t>
+          <t>https://www.indeed.com/viewjob?jk=afef76c3c4cb302e</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Applied Information Sciences</t>
+          <t>Anteriad</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Google Cloud Platform, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b4d756dafb24330</t>
+          <t>https://www.indeed.com/viewjob?jk=5a53981dcd494255</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr. Software Engineer II (DevOps)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bambee</t>
+          <t>Hi Marley</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Redshift, ECS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, DynamoDB, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e3ad167874c8532</t>
+          <t>https://www.indeed.com/viewjob?jk=57e6ba06d3a7b30f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>E T Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>World Bank Group</t>
+          <t>Applied Information Sciences</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, Splunk, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d019be2ca0c38b6</t>
+          <t>https://www.indeed.com/viewjob?jk=0b4d756dafb24330</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Systems Administrator</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Anduril</t>
+          <t>Bambee</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ashville, OH, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>Redshift, ECS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c796f5ba5948fe</t>
+          <t>https://www.indeed.com/viewjob?jk=3e3ad167874c8532</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Modem Machine Learning Engineer</t>
+          <t>E T Consultant</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>World Bank Group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,94 +1406,94 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63cf613962496b27</t>
+          <t>https://www.indeed.com/viewjob?jk=3d019be2ca0c38b6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Systems Administrator</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ICAT Logistics, Inc.</t>
+          <t>Anduril</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Ashville, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Lake Storage, GCP, BigQuery, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dfde2e65a7bc1cc</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c796f5ba5948fe</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Modem Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, dbt</t>
+          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60aa962ac2f33982</t>
+          <t>https://www.indeed.com/viewjob?jk=63cf613962496b27</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Services</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Crown Equipment</t>
+          <t>ICAT Logistics, Inc.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New Bremen, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Data Lake Storage, GCP, BigQuery, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=426a2df1dcd32427</t>
+          <t>https://www.indeed.com/viewjob?jk=7dfde2e65a7bc1cc</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Rediantt</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d3683730583b9c</t>
+          <t>https://www.indeed.com/viewjob?jk=60aa962ac2f33982</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Associate Data Engineer (REMOTE)</t>
+          <t>Data Engineer - Data Services</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Crown Equipment</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New Bremen, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f62c64972906caa0</t>
+          <t>https://www.indeed.com/viewjob?jk=426a2df1dcd32427</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Associate Data Engineer (REMOTE)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Rediantt</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad092c66101d7698</t>
+          <t>https://www.indeed.com/viewjob?jk=60d3683730583b9c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Cloud &amp; AI Platform [On-Site]</t>
+          <t>Associate Data Engineer (REMOTE)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7ba4a006c4d066d</t>
+          <t>https://www.indeed.com/viewjob?jk=f62c64972906caa0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Data Engineer (REMOTE)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,19 +1686,19 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7433f9b8b5c4a5a6</t>
+          <t>https://www.indeed.com/viewjob?jk=ad092c66101d7698</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer - Cloud &amp; AI Platform [On-Site]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, RDS, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddf7449abdd32b05</t>
+          <t>https://www.indeed.com/viewjob?jk=f7ba4a006c4d066d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Engineering and Analytics - USDS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Hadoop, HDFS, Hive, Flume, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b155ae7711afa6e</t>
+          <t>https://www.indeed.com/viewjob?jk=7433f9b8b5c4a5a6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI Engineering Intern</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Harvard Services Group, Inc</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Redshift, ECS, RDS, BigQuery, Snowflake, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a6b9d95984b1f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=ddf7449abdd32b05</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI Engineering Intern</t>
+          <t>Data Engineer, Data Engineering and Analytics - USDS</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Harvard Maintenance, Inc.</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Redshift, ECS, RDS, BigQuery, Snowflake, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
+          <t>AWS, S3, RDS, Hadoop, HDFS, Hive, Flume, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780346cd358075a8</t>
+          <t>https://www.indeed.com/viewjob?jk=5b155ae7711afa6e</t>
         </is>
       </c>
     </row>
@@ -1868,60 +1868,60 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer - Database</t>
+          <t>AI Engineering Intern</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TP-LINK</t>
+          <t>Harvard Services Group, Inc</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Cloud Storage, Scala, Kafka, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>Redshift, ECS, RDS, BigQuery, Snowflake, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c97fb5b4fe767905</t>
+          <t>https://www.indeed.com/viewjob?jk=9a6b9d95984b1f2d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineering Intern</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>Harvard Maintenance, Inc.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
+          <t>Redshift, ECS, RDS, BigQuery, Snowflake, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424fe727a6834d5b</t>
+          <t>https://www.indeed.com/viewjob?jk=780346cd358075a8</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Engineer</t>
+          <t>Senior Cloud Software Engineer - Database</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>TP-LINK</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Event Hubs, Snowflake, PostgreSQL, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, IAM, RDS, Cloud Storage, Scala, Kafka, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5cff3964beedb24</t>
+          <t>https://www.indeed.com/viewjob?jk=c97fb5b4fe767905</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, ML Platform | Parafin</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>carnaby fox</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, MLOps</t>
+          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4377663fa2ea1245</t>
+          <t>https://www.indeed.com/viewjob?jk=424fe727a6834d5b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer - III</t>
+          <t>Senior Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Noise Consulting Group</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Event Hubs, Snowflake, PostgreSQL, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2baa480224d46766</t>
+          <t>https://www.indeed.com/viewjob?jk=a5cff3964beedb24</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Engineering and Analytics - USDS</t>
+          <t>Senior Software Engineer, ML Platform | Parafin</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>carnaby fox</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Hadoop, HDFS, Hive, Flume, Spark, Scala, Kafka</t>
+          <t>AWS, Kinesis, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72ef2291619fe5e</t>
+          <t>https://www.indeed.com/viewjob?jk=4377663fa2ea1245</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack Developer</t>
+          <t>Data Engineer - III</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Benda Infotech</t>
+          <t>Noise Consulting Group</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c284602b40afa505</t>
+          <t>https://www.indeed.com/viewjob?jk=2baa480224d46766</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Data Engineer, Data Engineering and Analytics - USDS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Verification Technologies LLC</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Henderson, NV, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, Timestream, Step Functions, S3, SQS, API Gateway, IAM, RDS</t>
+          <t>AWS, S3, RDS, Hadoop, HDFS, Hive, Flume, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97a02535a97e1c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=d72ef2291619fe5e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior BI Analyst</t>
+          <t>Software Engineer - Full Stack Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Walker &amp; Dunlop</t>
+          <t>Benda Infotech</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=827ebbc8cea913b8</t>
+          <t>https://www.indeed.com/viewjob?jk=c284602b40afa505</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Point Wild</t>
+          <t>Verification Technologies LLC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Henderson, NV, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, Lambda, Athena, Timestream, Step Functions, S3, SQS, API Gateway, IAM, RDS</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,19 +2211,19 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e2022ce8366d457</t>
+          <t>https://www.indeed.com/viewjob?jk=97a02535a97e1c4c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior BI Analyst</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Point Wild</t>
+          <t>Walker &amp; Dunlop</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71457be51c270627</t>
+          <t>https://www.indeed.com/viewjob?jk=827ebbc8cea913b8</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccc6509aa3c8ec42</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2022ce8366d457</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8f514785edf8fdc</t>
+          <t>https://www.indeed.com/viewjob?jk=71457be51c270627</t>
         </is>
       </c>
     </row>
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f99d76959b32539</t>
+          <t>https://www.indeed.com/viewjob?jk=ccc6509aa3c8ec42</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Analytical Engineer, Payment Data Intelligence - USDS</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Point Wild</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a567c2b339c20c2f</t>
+          <t>https://www.indeed.com/viewjob?jk=d8f514785edf8fdc</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Azure Databricks Platform Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Point Wild</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Event Hubs, Medallion Architecture, Spark, PySpark, SQL Server, Data Modeling</t>
+          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=809ad06a2b50c327</t>
+          <t>https://www.indeed.com/viewjob?jk=7f99d76959b32539</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI ML Data Scientist</t>
+          <t>Data Analytical Engineer, Payment Data Intelligence - USDS</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Westlake Village, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Azure, Hadoop, YARN, Spark, PySpark, Kafka, Oracle, NoSQL, Tableau, Docker</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce609bae5ee0d5a2</t>
+          <t>https://www.indeed.com/viewjob?jk=a567c2b339c20c2f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Development Engineer â€“ Backend / Platform</t>
+          <t>Azure Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Sinclair Broadcast Group</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Event Hubs, Medallion Architecture, Spark, PySpark, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41a635808e4af271</t>
+          <t>https://www.indeed.com/viewjob?jk=809ad06a2b50c327</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS</t>
+          <t>AI ML Data Scientist</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Westlake Village, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, ELT, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>Azure, Hadoop, YARN, Spark, PySpark, Kafka, Oracle, NoSQL, Tableau, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bce752ad6855e523</t>
+          <t>https://www.indeed.com/viewjob?jk=ce609bae5ee0d5a2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DevX / Developer Operations (Partner 16, Partner 18), ASG</t>
+          <t>Software Development Engineer â€“ Backend / Platform</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Andreessen Horowitz</t>
+          <t>Sinclair Broadcast Group</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>Kinesis, IAM, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2570942407162c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=41a635808e4af271</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Site Reliability Engineer</t>
+          <t>Software Engineering SMTS</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, ELT, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e4b910ec252456f</t>
+          <t>https://www.indeed.com/viewjob?jk=bce752ad6855e523</t>
         </is>
       </c>
     </row>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>a16z</t>
+          <t>Andreessen Horowitz</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0f26d4983647c6b</t>
+          <t>https://www.indeed.com/viewjob?jk=2570942407162c4a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>Software Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Vytl Controls Group</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f97f2d7c736b559</t>
+          <t>https://www.indeed.com/viewjob?jk=8e4b910ec252456f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Informatica ETL Developer - 6326296</t>
+          <t>DevX / Developer Operations (Partner 16, Partner 18), ASG</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>a16z</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1a17c04578e9be3</t>
+          <t>https://www.indeed.com/viewjob?jk=e0f26d4983647c6b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Informatica ETL Developer - 6326296</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Vytl Controls Group</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, Git</t>
+          <t>RDS, Azure, Databricks, Scala, SQL Server, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21eab84e17f0b1ac</t>
+          <t>https://www.indeed.com/viewjob?jk=2f97f2d7c736b559</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer III</t>
+          <t>Informatica ETL Developer - 6326296</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, MLflow, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b58a2b9f1b9c3a51</t>
+          <t>https://www.indeed.com/viewjob?jk=e1a17c04578e9be3</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Privacy &amp; Infrastructure - USDS</t>
+          <t>Informatica ETL Developer - 6326296</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, HDFS, Hive, Spark, Kafka, MySQL, NoSQL, Kubernetes</t>
+          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=625f5552fcee590f</t>
+          <t>https://www.indeed.com/viewjob?jk=21eab84e17f0b1ac</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Machine Learning Engineer III</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, SQS, API Gateway, ECS, RDS, Jenkins</t>
+          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, MLflow, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e888182752c6207b</t>
+          <t>https://www.indeed.com/viewjob?jk=b58a2b9f1b9c3a51</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Software Engineer, Data Privacy &amp; Infrastructure - USDS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ERP SAVVY LLC</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Skillman, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Oozie, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, Power BI</t>
+          <t>AWS, IAM, RDS, HDFS, Hive, Spark, Kafka, MySQL, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a04b59dd3c9c139</t>
+          <t>https://www.indeed.com/viewjob?jk=625f5552fcee590f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Digital Native Business</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, SQS, API Gateway, ECS, RDS, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dec276bec6c38a67</t>
+          <t>https://www.indeed.com/viewjob?jk=e888182752c6207b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Digital Native Business</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>ERP SAVVY LLC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Skillman, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>Hadoop, HDFS, Oozie, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377873b4a91a42db</t>
+          <t>https://www.indeed.com/viewjob?jk=8a04b59dd3c9c139</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Resident Solutions Architect - Digital Native Business</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=936e44ddac734d7b</t>
+          <t>https://www.indeed.com/viewjob?jk=dec276bec6c38a67</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer - AI Forward Engineer</t>
+          <t>Resident Solutions Architect - Digital Native Business</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CarParts.com</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81e7e89cef9a97da</t>
+          <t>https://www.indeed.com/viewjob?jk=377873b4a91a42db</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Safelease</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6884b300f1b32ae4</t>
+          <t>https://www.indeed.com/viewjob?jk=936e44ddac734d7b</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Full Stack Engineer - AI Forward Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>CarParts.com</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1849a5b7a2f2af9b</t>
+          <t>https://www.indeed.com/viewjob?jk=81e7e89cef9a97da</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Java Developer (Connected Services)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Safelease</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa3dcc861e4ac768</t>
+          <t>https://www.indeed.com/viewjob?jk=6884b300f1b32ae4</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer, Application Development</t>
+          <t>Java Developer (Connected Services)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e58bc4277f70431</t>
+          <t>https://www.indeed.com/viewjob?jk=fa3dcc861e4ac768</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fea29a3880a03255</t>
+          <t>https://www.indeed.com/viewjob?jk=4e58bc4277f70431</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb3cb19cae9db9b</t>
+          <t>https://www.indeed.com/viewjob?jk=fea29a3880a03255</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer Fish Data Systems</t>
+          <t>Full Stack Senior Engineer, Application Development</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PACIFIC STATES MARINE FISHERIES COMMISSION</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Oracle, SQL Server, PostgreSQL, ELT, Power BI, CI/CD, Docker</t>
+          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b90c3fac511dfb2</t>
+          <t>https://www.indeed.com/viewjob?jk=3bb3cb19cae9db9b</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Full Stack Cloud Engineer</t>
+          <t>Full Stack Software Engineer Fish Data Systems</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>The Akanksha LLC</t>
+          <t>PACIFIC STATES MARINE FISHERIES COMMISSION</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Azure, Data Factory, Oracle, SQL Server, PostgreSQL, ELT, Power BI, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaf16acc114cd913</t>
+          <t>https://www.indeed.com/viewjob?jk=0b90c3fac511dfb2</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Scientific System of Record</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Medallion Architecture, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a083efe79b22465</t>
+          <t>https://www.indeed.com/viewjob?jk=1849a5b7a2f2af9b</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Scientific System of Record</t>
+          <t>Full Stack Cloud Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>The Akanksha LLC</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, API Gateway, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,67 +3366,67 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=233d27bbc07fd70f</t>
+          <t>https://www.indeed.com/viewjob?jk=aaf16acc114cd913</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Consultant – Data Engineer &amp; GovernanceNew</t>
+          <t>Senior Software Engineer, Scientific System of Record</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Quisitive</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69dc7b2b5de56422</t>
+          <t>https://www.indeed.com/viewjob?jk=0a083efe79b22465</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Senior Software Engineer, Scientific System of Record</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,14 +3436,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=226e96da47ff2b1a</t>
+          <t>https://www.indeed.com/viewjob?jk=233d27bbc07fd70f</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Consultant – Data Engineer &amp; Governance</t>
+          <t>Senior Data Consultant – Data Engineer &amp; GovernanceNew</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3466,29 +3466,29 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd77d29cb01573c</t>
+          <t>https://www.indeed.com/viewjob?jk=69dc7b2b5de56422</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer â€“ Python/AI</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb44a4b768419ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=226e96da47ff2b1a</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer - Finance Modernization</t>
+          <t>Senior Data Consultant – Data Engineer &amp; Governance</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Quisitive</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Spark, Scala, CI/CD, Terraform, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ee917ec6e025e8</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd77d29cb01573c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Salesforce Technical Architect, Data &amp; AI</t>
+          <t>Data Engineer â€“ Python/AI</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>NeuraFlash, Part of Accenture</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Redshift, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Git</t>
+          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3420dddc661e222d</t>
+          <t>https://www.indeed.com/viewjob?jk=bb44a4b768419ca2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Software Engineer - Finance Modernization</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Zookeeper, Scala, Kafka, Oracle, CI/CD</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Spark, Scala, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d5b2e7bc490d9bd</t>
+          <t>https://www.indeed.com/viewjob?jk=15ee917ec6e025e8</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Model Risk Management</t>
+          <t>Salesforce Technical Architect, Data &amp; AI</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>NeuraFlash, Part of Accenture</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Vertex AI, Snowflake, ETL, MLflow, pytest, Git</t>
+          <t>AWS, Redshift, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4b8c7a56e0e088</t>
+          <t>https://www.indeed.com/viewjob?jk=3420dddc661e222d</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AI LLM Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Siemens Healthineers</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, Data Modeling, ELT, Power BI, Git, Python</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Zookeeper, Scala, Kafka, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77cc10c4736bb6e5</t>
+          <t>https://www.indeed.com/viewjob?jk=3d5b2e7bc490d9bd</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Lakebase Sales Specialist- Financial Services</t>
+          <t>Senior Machine Learning Engineer, Model Risk Management</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, GCP, Vertex AI, Snowflake, ETL, MLflow, pytest, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d86224c98360290</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4b8c7a56e0e088</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>AI LLM Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Siemens Healthineers</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Spark, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, Data Modeling, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a874d216618930</t>
+          <t>https://www.indeed.com/viewjob?jk=77cc10c4736bb6e5</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AI Software Engineer - Center for Diagnostics and Artificial Intelligence</t>
+          <t>Lakebase Sales Specialist- Financial Services</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Cleveland Clinic</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10aaff122c10f274</t>
+          <t>https://www.indeed.com/viewjob?jk=6d86224c98360290</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SAS Developer (with Admin Background)</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, ETL, CI/CD, Git</t>
+          <t>Redshift, Databricks, BigQuery, Spark, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f708bb2089c8e37e</t>
+          <t>https://www.indeed.com/viewjob?jk=90a874d216618930</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SAS Developer (with Admin Background)</t>
+          <t>AI Software Engineer - Center for Diagnostics and Artificial Intelligence</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cleveland Clinic</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, ETL, CI/CD, Git</t>
+          <t>S3, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b030dd9a627fd2c</t>
+          <t>https://www.indeed.com/viewjob?jk=10aaff122c10f274</t>
         </is>
       </c>
     </row>
@@ -3898,17 +3898,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer - Analytics</t>
+          <t>Sr. Software Engineer (React/Typescript)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>EvergreenHealth</t>
+          <t>Vertafore</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, Star Schema, ETL, Power BI, Tableau, Azure DevOps, Git</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=847c2fe533f1ec86</t>
+          <t>https://www.indeed.com/viewjob?jk=757afec97d5d27e0</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (React/Typescript)</t>
+          <t>Data Engineer - Java - Loops</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Vertafore</t>
+          <t>Copperleaf Technologies Inc.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Git, Datadog</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=757afec97d5d27e0</t>
+          <t>https://www.indeed.com/viewjob?jk=fe4ff78e6fcedc19</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Engineer - Java - Loops</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Copperleaf Technologies Inc.</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Git, Datadog</t>
+          <t>RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Splunk, CI/CD, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe4ff78e6fcedc19</t>
+          <t>https://www.indeed.com/viewjob?jk=d604ebca572d9a0d</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d604ebca572d9a0d</t>
+          <t>https://www.indeed.com/viewjob?jk=244f96a693bca9f8</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=244f96a693bca9f8</t>
+          <t>https://www.indeed.com/viewjob?jk=4229f7f9f0a4e0f7</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>SAS Developer (with Admin Background)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Splunk, CI/CD, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,7 +4101,77 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4229f7f9f0a4e0f7</t>
+          <t>https://www.indeed.com/viewjob?jk=f708bb2089c8e37e</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>SAS Developer (with Admin Background)</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, ETL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b030dd9a627fd2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Business Intelligence Developer - Analytics</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>EvergreenHealth</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Kirkland, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Data Modeling, Star Schema, ETL, Power BI, Tableau, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=847c2fe533f1ec86</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-04.xlsx
+++ b/results/job_matches_2026-06-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Platform</t>
+          <t>Software Developer II - Meter Data Management Software (Full Stack, Databricks)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,34 +521,34 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Databricks, Unity Catalog, Spark</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526f04da000b8153</t>
+          <t>https://www.indeed.com/viewjob?jk=3267639dd0ee93d7</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ETL/ELT Developer</t>
+          <t>Software Engineer III - Data Platform</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AEM Corporation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Databricks, Unity Catalog, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4c2c00b592047da</t>
+          <t>https://www.indeed.com/viewjob?jk=526f04da000b8153</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer IV</t>
+          <t>ETL/ELT Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Airlines Reporting Corporation (ARC)</t>
+          <t>AEM Corporation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98137df2f9a11a45</t>
+          <t>https://www.indeed.com/viewjob?jk=a4c2c00b592047da</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. AWS Data Engineer</t>
+          <t>Data Engineer IV</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Airlines Reporting Corporation (ARC)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Hadoop</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d62532bd79c16947</t>
+          <t>https://www.indeed.com/viewjob?jk=98137df2f9a11a45</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
+          <t>Sr. AWS Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Hadoop</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9f4e94883170da4</t>
+          <t>https://www.indeed.com/viewjob?jk=d62532bd79c16947</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior ETL Developer (Azure &amp; MDM/Reltio Focus)</t>
+          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Duncan, SC, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feaf489696c6ebd7</t>
+          <t>https://www.indeed.com/viewjob?jk=b9f4e94883170da4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AWS Engineer - ML</t>
+          <t>Senior ETL Developer (Azure &amp; MDM/Reltio Focus)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Duncan, SC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e808d31f6fa032cf</t>
+          <t>https://www.indeed.com/viewjob?jk=feaf489696c6ebd7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AWS Engineer - ML</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac18de92e2d0da2c</t>
+          <t>https://www.indeed.com/viewjob?jk=e808d31f6fa032cf</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
+          <t>AWS, Glue, Redshift, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d784ad2795e0379d</t>
+          <t>https://www.indeed.com/viewjob?jk=ac18de92e2d0da2c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Engineer - Data</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tunnl</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, RDS, Scala, DynamoDB, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b66532c29a2d2fb3</t>
+          <t>https://www.indeed.com/viewjob?jk=d784ad2795e0379d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior ETL Developer (Azure &amp; MDM/Reltio Focus)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>Tunnl</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Duncan, SC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, RDS, Scala, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bde84b2e0c4d7b5</t>
+          <t>https://www.indeed.com/viewjob?jk=b66532c29a2d2fb3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Information Technology - BI Developer</t>
+          <t>Senior ETL Developer (Azure &amp; MDM/Reltio Focus)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TCC Verizon Authorized Retailer</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fishers, IN, US USA</t>
+          <t>Duncan, SC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,42 +906,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad7533e66ad7d7d8</t>
+          <t>https://www.indeed.com/viewjob?jk=6bde84b2e0c4d7b5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Developer I - Data Engineer</t>
+          <t>Information Technology - BI Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>TCC Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fishers, IN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, Kafka, Polars, Snowflake, Star Schema, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4e3803b26dd25a2</t>
+          <t>https://www.indeed.com/viewjob?jk=ad7533e66ad7d7d8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer, Security &amp; Information Technology - USDS</t>
+          <t>Senior Developer I - Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Azure, Spark, Scala, Kafka, Polars, Snowflake, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8131bdacb963c45</t>
+          <t>https://www.indeed.com/viewjob?jk=b4e3803b26dd25a2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Automation Platform Engineer</t>
+          <t>Full Stack Software Engineer, Security &amp; Information Technology - USDS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Littleton, CO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, AWS CodePipeline, Terraform, Docker, Kubernetes</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc94922007c35c18</t>
+          <t>https://www.indeed.com/viewjob?jk=b8131bdacb963c45</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Automation Architect – AI, Cloud &amp; Quality Engineering</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ICAT Logistics, Inc.</t>
+          <t>BridgeNexus Technologies Inc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, SQS, Azure, Scala, PostgreSQL, MongoDB, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=490396287ca9423d</t>
+          <t>https://www.indeed.com/viewjob?jk=8019de144986634a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior Automation Platform Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, AWS CodePipeline, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eba11dc550c0d956</t>
+          <t>https://www.indeed.com/viewjob?jk=bc94922007c35c18</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>ICAT Logistics, Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eea1d0eeb00ba384</t>
+          <t>https://www.indeed.com/viewjob?jk=490396287ca9423d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Python Data Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,69 +1151,69 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Hadoop, HDFS, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da84632d9568dfce</t>
+          <t>https://www.indeed.com/viewjob?jk=eba11dc550c0d956</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Python Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, Azure, GCP, Hadoop, HDFS, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=336bfe0af38918a1</t>
+          <t>https://www.indeed.com/viewjob?jk=da84632d9568dfce</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior AWS Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SIGNITIVES</t>
+          <t>Teachers Retirement System</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afef76c3c4cb302e</t>
+          <t>https://www.indeed.com/viewjob?jk=fdb97cb6b9e8a913</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Anteriad</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Google Cloud Platform, Dataflow, Cloud Storage, Spark</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a53981dcd494255</t>
+          <t>https://www.indeed.com/viewjob?jk=336bfe0af38918a1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II (DevOps)</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hi Marley</t>
+          <t>SIGNITIVES</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, DynamoDB, ETL, ELT</t>
+          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57e6ba06d3a7b30f</t>
+          <t>https://www.indeed.com/viewjob?jk=afef76c3c4cb302e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Applied Information Sciences</t>
+          <t>Bambee</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>Redshift, ECS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b4d756dafb24330</t>
+          <t>https://www.indeed.com/viewjob?jk=3e3ad167874c8532</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Modem Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bambee</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Redshift, ECS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,129 +1371,129 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e3ad167874c8532</t>
+          <t>https://www.indeed.com/viewjob?jk=63cf613962496b27</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>E T Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>World Bank Group</t>
+          <t>ICAT Logistics, Inc.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, Splunk, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Data Lake Storage, GCP, BigQuery, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d019be2ca0c38b6</t>
+          <t>https://www.indeed.com/viewjob?jk=7dfde2e65a7bc1cc</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Systems Administrator</t>
+          <t>Data Engineer - Data Services</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Anduril</t>
+          <t>Crown Equipment</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ashville, OH, US USA</t>
+          <t>New Bremen, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c796f5ba5948fe</t>
+          <t>https://www.indeed.com/viewjob?jk=426a2df1dcd32427</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Modem Machine Learning Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Rediantt</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63cf613962496b27</t>
+          <t>https://www.indeed.com/viewjob?jk=60d3683730583b9c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Data Engineer (REMOTE)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ICAT Logistics, Inc.</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Lake Storage, GCP, BigQuery, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dfde2e65a7bc1cc</t>
+          <t>https://www.indeed.com/viewjob?jk=f62c64972906caa0</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Data Engineer (REMOTE)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, dbt</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60aa962ac2f33982</t>
+          <t>https://www.indeed.com/viewjob?jk=ad092c66101d7698</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Services</t>
+          <t>Sr. Data Engineer - Cloud &amp; AI Platform [On-Site]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Crown Equipment</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New Bremen, OH, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD</t>
+          <t>AWS, Glue, EMR, RDS, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=426a2df1dcd32427</t>
+          <t>https://www.indeed.com/viewjob?jk=f7ba4a006c4d066d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer, Data Engineering and Analytics - USDS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Rediantt</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, S3, RDS, Hadoop, HDFS, Hive, Flume, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,19 +1616,19 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d3683730583b9c</t>
+          <t>https://www.indeed.com/viewjob?jk=5b155ae7711afa6e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Associate Data Engineer (REMOTE)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Darkk Alpha Capital</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f62c64972906caa0</t>
+          <t>https://www.indeed.com/viewjob?jk=f68d653a407d3790</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Associate Data Engineer (REMOTE)</t>
+          <t>AI Engineering Intern</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Harvard Services Group, Inc</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>Redshift, ECS, RDS, BigQuery, Snowflake, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad092c66101d7698</t>
+          <t>https://www.indeed.com/viewjob?jk=9a6b9d95984b1f2d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Cloud &amp; AI Platform [On-Site]</t>
+          <t>AI Engineering Intern</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Harvard Maintenance, Inc.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>Redshift, ECS, RDS, BigQuery, Snowflake, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,42 +1721,42 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7ba4a006c4d066d</t>
+          <t>https://www.indeed.com/viewjob?jk=780346cd358075a8</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Software Engineer - Database</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>TP-LINK</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, IAM, RDS, Cloud Storage, Scala, Kafka, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7433f9b8b5c4a5a6</t>
+          <t>https://www.indeed.com/viewjob?jk=c97fb5b4fe767905</t>
         </is>
       </c>
     </row>
@@ -1768,20 +1768,20 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddf7449abdd32b05</t>
+          <t>https://www.indeed.com/viewjob?jk=424fe727a6834d5b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Engineering and Analytics - USDS</t>
+          <t>Senior Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Hadoop, HDFS, Hive, Flume, Spark, Scala, Kafka</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Event Hubs, Snowflake, PostgreSQL, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b155ae7711afa6e</t>
+          <t>https://www.indeed.com/viewjob?jk=a5cff3964beedb24</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (contract)</t>
+          <t>Data Engineer, Data Engineering and Analytics - USDS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Kafka, Oracle, MongoDB, Splunk, Jenkins</t>
+          <t>AWS, S3, RDS, Hadoop, HDFS, Hive, Flume, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26d05b8ec42e7cf9</t>
+          <t>https://www.indeed.com/viewjob?jk=d72ef2291619fe5e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Engineering Intern</t>
+          <t>Software Engineer - Full Stack Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Harvard Services Group, Inc</t>
+          <t>Benda Infotech</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Redshift, ECS, RDS, BigQuery, Snowflake, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a6b9d95984b1f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=c284602b40afa505</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Engineering Intern</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Harvard Maintenance, Inc.</t>
+          <t>Verification Technologies LLC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Henderson, NV, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Redshift, ECS, RDS, BigQuery, Snowflake, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
+          <t>AWS, Lambda, Athena, Timestream, Step Functions, S3, SQS, API Gateway, IAM, RDS</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780346cd358075a8</t>
+          <t>https://www.indeed.com/viewjob?jk=97a02535a97e1c4c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer - Database</t>
+          <t>Senior BI Analyst</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>TP-LINK</t>
+          <t>Walker &amp; Dunlop</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Cloud Storage, Scala, Kafka, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c97fb5b4fe767905</t>
+          <t>https://www.indeed.com/viewjob?jk=827ebbc8cea913b8</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>Point Wild</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424fe727a6834d5b</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2022ce8366d457</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Point Wild</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Event Hubs, Snowflake, PostgreSQL, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5cff3964beedb24</t>
+          <t>https://www.indeed.com/viewjob?jk=71457be51c270627</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, ML Platform | Parafin</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>carnaby fox</t>
+          <t>Point Wild</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, MLOps</t>
+          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4377663fa2ea1245</t>
+          <t>https://www.indeed.com/viewjob?jk=ccc6509aa3c8ec42</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer - III</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Noise Consulting Group</t>
+          <t>Point Wild</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2baa480224d46766</t>
+          <t>https://www.indeed.com/viewjob?jk=d8f514785edf8fdc</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Engineering and Analytics - USDS</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Point Wild</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Hadoop, HDFS, Hive, Flume, Spark, Scala, Kafka</t>
+          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72ef2291619fe5e</t>
+          <t>https://www.indeed.com/viewjob?jk=7f99d76959b32539</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack Developer</t>
+          <t>Data Analytical Engineer, Payment Data Intelligence - USDS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Benda Infotech</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c284602b40afa505</t>
+          <t>https://www.indeed.com/viewjob?jk=a567c2b339c20c2f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Azure Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Verification Technologies LLC</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Henderson, NV, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, Timestream, Step Functions, S3, SQS, API Gateway, IAM, RDS</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Event Hubs, Medallion Architecture, Spark, PySpark, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97a02535a97e1c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=809ad06a2b50c327</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior BI Analyst</t>
+          <t>AI ML Data Scientist</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Walker &amp; Dunlop</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westlake Village, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>Azure, Hadoop, YARN, Spark, PySpark, Kafka, Oracle, NoSQL, Tableau, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=827ebbc8cea913b8</t>
+          <t>https://www.indeed.com/viewjob?jk=ce609bae5ee0d5a2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>DevX / Developer Operations (Partner 16, Partner 18), ASG</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Point Wild</t>
+          <t>Andreessen Horowitz</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e2022ce8366d457</t>
+          <t>https://www.indeed.com/viewjob?jk=2570942407162c4a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Point Wild</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71457be51c270627</t>
+          <t>https://www.indeed.com/viewjob?jk=8e4b910ec252456f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>DevX / Developer Operations (Partner 16, Partner 18), ASG</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Point Wild</t>
+          <t>a16z</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccc6509aa3c8ec42</t>
+          <t>https://www.indeed.com/viewjob?jk=e0f26d4983647c6b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineering SMTS</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Point Wild</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Scala, ELT, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8f514785edf8fdc</t>
+          <t>https://www.indeed.com/viewjob?jk=bce752ad6855e523</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Point Wild</t>
+          <t>Vytl Controls Group</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Databricks, Scala, SQL Server, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f99d76959b32539</t>
+          <t>https://www.indeed.com/viewjob?jk=2f97f2d7c736b559</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Analytical Engineer, Payment Data Intelligence - USDS</t>
+          <t>Informatica ETL Developer - 6326296</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a567c2b339c20c2f</t>
+          <t>https://www.indeed.com/viewjob?jk=e1a17c04578e9be3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Azure Databricks Platform Engineer</t>
+          <t>Informatica ETL Developer - 6326296</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Event Hubs, Medallion Architecture, Spark, PySpark, SQL Server, Data Modeling</t>
+          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,67 +2491,67 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=809ad06a2b50c327</t>
+          <t>https://www.indeed.com/viewjob?jk=21eab84e17f0b1ac</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI ML Data Scientist</t>
+          <t>Machine Learning Engineer III</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Westlake Village, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, Hadoop, YARN, Spark, PySpark, Kafka, Oracle, NoSQL, Tableau, Docker</t>
+          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, MLflow, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce609bae5ee0d5a2</t>
+          <t>https://www.indeed.com/viewjob?jk=b58a2b9f1b9c3a51</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Development Engineer â€“ Backend / Platform</t>
+          <t>Software Engineer, Data Privacy &amp; Infrastructure - USDS</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Sinclair Broadcast Group</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, HDFS, Hive, Spark, Kafka, MySQL, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,164 +2561,164 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41a635808e4af271</t>
+          <t>https://www.indeed.com/viewjob?jk=625f5552fcee590f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, ELT, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, SQS, API Gateway, ECS, RDS, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bce752ad6855e523</t>
+          <t>https://www.indeed.com/viewjob?jk=e888182752c6207b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DevX / Developer Operations (Partner 16, Partner 18), ASG</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Andreessen Horowitz</t>
+          <t>ERP SAVVY LLC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Skillman, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>Hadoop, HDFS, Oozie, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2570942407162c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=8a04b59dd3c9c139</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Site Reliability Engineer</t>
+          <t>Resident Solutions Architect - Digital Native Business</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e4b910ec252456f</t>
+          <t>https://www.indeed.com/viewjob?jk=dec276bec6c38a67</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DevX / Developer Operations (Partner 16, Partner 18), ASG</t>
+          <t>Resident Solutions Architect - Digital Native Business</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>a16z</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0f26d4983647c6b</t>
+          <t>https://www.indeed.com/viewjob?jk=377873b4a91a42db</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>Sr. Full Stack Engineer - AI Forward Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Vytl Controls Group</t>
+          <t>CarParts.com</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f97f2d7c736b559</t>
+          <t>https://www.indeed.com/viewjob?jk=81e7e89cef9a97da</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Informatica ETL Developer - 6326296</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, Git</t>
+          <t>RDS, Azure, Medallion Architecture, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1a17c04578e9be3</t>
+          <t>https://www.indeed.com/viewjob?jk=1849a5b7a2f2af9b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Informatica ETL Developer - 6326296</t>
+          <t>Java Developer (Connected Services)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, Git</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21eab84e17f0b1ac</t>
+          <t>https://www.indeed.com/viewjob?jk=fa3dcc861e4ac768</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer III</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, MLflow, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b58a2b9f1b9c3a51</t>
+          <t>https://www.indeed.com/viewjob?jk=936e44ddac734d7b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Privacy &amp; Infrastructure - USDS</t>
+          <t>Full Stack Senior Engineer, Application Development</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, HDFS, Hive, Spark, Kafka, MySQL, NoSQL, Kubernetes</t>
+          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=625f5552fcee590f</t>
+          <t>https://www.indeed.com/viewjob?jk=4e58bc4277f70431</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Full Stack Senior Engineer, Application Development</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, SQS, API Gateway, ECS, RDS, Jenkins</t>
+          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e888182752c6207b</t>
+          <t>https://www.indeed.com/viewjob?jk=fea29a3880a03255</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Full Stack Senior Engineer, Application Development</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ERP SAVVY LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Skillman, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Oozie, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, Power BI</t>
+          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a04b59dd3c9c139</t>
+          <t>https://www.indeed.com/viewjob?jk=3bb3cb19cae9db9b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Digital Native Business</t>
+          <t>Full Stack Software Engineer Fish Data Systems</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>PACIFIC STATES MARINE FISHERIES COMMISSION</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Data Factory, Oracle, SQL Server, PostgreSQL, ELT, Power BI, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dec276bec6c38a67</t>
+          <t>https://www.indeed.com/viewjob?jk=0b90c3fac511dfb2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Digital Native Business</t>
+          <t>Full Stack Cloud Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>The Akanksha LLC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,42 +3006,42 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Lambda, API Gateway, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377873b4a91a42db</t>
+          <t>https://www.indeed.com/viewjob?jk=aaf16acc114cd913</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,67 +3051,67 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=936e44ddac734d7b</t>
+          <t>https://www.indeed.com/viewjob?jk=226e96da47ff2b1a</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer - AI Forward Engineer</t>
+          <t>Senior Data Consultant – Data Engineer &amp; Governance</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CarParts.com</t>
+          <t>Quisitive</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81e7e89cef9a97da</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd77d29cb01573c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer â€“ Python/AI</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Safelease</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6884b300f1b32ae4</t>
+          <t>https://www.indeed.com/viewjob?jk=bb44a4b768419ca2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Java Developer (Connected Services)</t>
+          <t>Software Engineer - Finance Modernization</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Spark, Scala, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,172 +3156,172 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa3dcc861e4ac768</t>
+          <t>https://www.indeed.com/viewjob?jk=15ee917ec6e025e8</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer, Application Development</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>endava</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e58bc4277f70431</t>
+          <t>https://www.indeed.com/viewjob?jk=163d2dba42ea7b46</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer, Application Development</t>
+          <t>Salesforce Technical Architect, Data &amp; AI</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NeuraFlash, Part of Accenture</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Redshift, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fea29a3880a03255</t>
+          <t>https://www.indeed.com/viewjob?jk=3420dddc661e222d</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer, Application Development</t>
+          <t>Senior DevOps/MLOps Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Algorized</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Campbell, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, S3, ECS, IAM, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb3cb19cae9db9b</t>
+          <t>https://www.indeed.com/viewjob?jk=0c88a8d02f220104</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer Fish Data Systems</t>
+          <t>Senior Specialist - Quality Engineering</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PACIFIC STATES MARINE FISHERIES COMMISSION</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Oracle, SQL Server, PostgreSQL, ELT, Power BI, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b90c3fac511dfb2</t>
+          <t>https://www.indeed.com/viewjob?jk=53ced3da28996aca</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Machine Learning Engineer, Model Risk Management</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, GCP, Vertex AI, Snowflake, ETL, MLflow, pytest, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1849a5b7a2f2af9b</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4b8c7a56e0e088</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Full Stack Cloud Engineer</t>
+          <t>AI LLM Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>The Akanksha LLC</t>
+          <t>Siemens Healthineers</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, Data Modeling, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaf16acc114cd913</t>
+          <t>https://www.indeed.com/viewjob?jk=77cc10c4736bb6e5</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Scientific System of Record</t>
+          <t>Lakebase Sales Specialist- Financial Services</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a083efe79b22465</t>
+          <t>https://www.indeed.com/viewjob?jk=6d86224c98360290</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Scientific System of Record</t>
+          <t>SAS Developer (with Admin Background)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=233d27bbc07fd70f</t>
+          <t>https://www.indeed.com/viewjob?jk=f708bb2089c8e37e</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Consultant – Data Engineer &amp; GovernanceNew</t>
+          <t>SAS Developer (with Admin Background)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Quisitive</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69dc7b2b5de56422</t>
+          <t>https://www.indeed.com/viewjob?jk=2b030dd9a627fd2c</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>Azure, Medallion Architecture, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=226e96da47ff2b1a</t>
+          <t>https://www.indeed.com/viewjob?jk=e8d59fd93890be9a</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Consultant – Data Engineer &amp; Governance</t>
+          <t>Business Intelligence Developer - Analytics</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Quisitive</t>
+          <t>EvergreenHealth</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Data Modeling, Star Schema, ETL, Power BI, Tableau, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd77d29cb01573c</t>
+          <t>https://www.indeed.com/viewjob?jk=847c2fe533f1ec86</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer â€“ Python/AI</t>
+          <t>Sr. Software Engineer (React/Typescript)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Vertafore</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb44a4b768419ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=757afec97d5d27e0</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer - Finance Modernization</t>
+          <t>Data Engineer - Java - Loops</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Copperleaf Technologies Inc.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Spark, Scala, CI/CD, Terraform, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Git, Datadog</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ee917ec6e025e8</t>
+          <t>https://www.indeed.com/viewjob?jk=fe4ff78e6fcedc19</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Salesforce Technical Architect, Data &amp; AI</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>NeuraFlash, Part of Accenture</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Redshift, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Git</t>
+          <t>RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Splunk, CI/CD, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3420dddc661e222d</t>
+          <t>https://www.indeed.com/viewjob?jk=d604ebca572d9a0d</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Zookeeper, Scala, Kafka, Oracle, CI/CD</t>
+          <t>RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Splunk, CI/CD, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d5b2e7bc490d9bd</t>
+          <t>https://www.indeed.com/viewjob?jk=244f96a693bca9f8</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Model Risk Management</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Vertex AI, Snowflake, ETL, MLflow, pytest, Git</t>
+          <t>RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Splunk, CI/CD, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,462 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4b8c7a56e0e088</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>AI LLM Engineer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Siemens Healthineers</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, Data Modeling, ELT, Power BI, Git, Python</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=77cc10c4736bb6e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Lakebase Sales Specialist- Financial Services</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6d86224c98360290</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Solution Architect</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Sigma Computing</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Redshift, Databricks, BigQuery, Spark, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=90a874d216618930</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>AI Software Engineer - Center for Diagnostics and Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Cleveland Clinic</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Cleveland, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>S3, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=10aaff122c10f274</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Expleo Group</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Azure, Medallion Architecture, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e8d59fd93890be9a</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer (React/Typescript)</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Vertafore</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=757afec97d5d27e0</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Data Engineer - Java - Loops</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Copperleaf Technologies Inc.</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe4ff78e6fcedc19</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Splunk, CI/CD, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d604ebca572d9a0d</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>West Des Moines, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Splunk, CI/CD, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=244f96a693bca9f8</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Splunk, CI/CD, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=4229f7f9f0a4e0f7</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>SAS Developer (with Admin Background)</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f708bb2089c8e37e</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>SAS Developer (with Admin Background)</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2b030dd9a627fd2c</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer - Analytics</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>EvergreenHealth</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Kirkland, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Data Modeling, Star Schema, ETL, Power BI, Tableau, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=847c2fe533f1ec86</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-04.xlsx
+++ b/results/job_matches_2026-06-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,87 +538,87 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Platform</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BONbLOC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Databricks, Unity Catalog, Spark</t>
+          <t>AWS, Glue, EMR, Redshift, S3, RDS, Google Cloud Platform, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526f04da000b8153</t>
+          <t>https://www.indeed.com/viewjob?jk=203332422aec13ef</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ETL/ELT Developer</t>
+          <t>AI Applied Architect (.NET &amp; Databricks)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AEM Corporation</t>
+          <t>Symhas</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4c2c00b592047da</t>
+          <t>https://www.indeed.com/viewjob?jk=c3c1f686434a6c4c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer IV</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Airlines Reporting Corporation (ARC)</t>
+          <t>Decision Foundry</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, API Gateway, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98137df2f9a11a45</t>
+          <t>https://www.indeed.com/viewjob?jk=4373bea89867ea0b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. AWS Data Engineer</t>
+          <t>Data Engineer IV</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Airlines Reporting Corporation (ARC)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Hadoop</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d62532bd79c16947</t>
+          <t>https://www.indeed.com/viewjob?jk=98137df2f9a11a45</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
+          <t>Sr. AWS Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Hadoop</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9f4e94883170da4</t>
+          <t>https://www.indeed.com/viewjob?jk=d62532bd79c16947</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior ETL Developer (Azure &amp; MDM/Reltio Focus)</t>
+          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Duncan, SC, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feaf489696c6ebd7</t>
+          <t>https://www.indeed.com/viewjob?jk=b9f4e94883170da4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AWS Engineer - ML</t>
+          <t>Senior ETL Developer (Azure &amp; MDM/Reltio Focus)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Duncan, SC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e808d31f6fa032cf</t>
+          <t>https://www.indeed.com/viewjob?jk=feaf489696c6ebd7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>DevIQ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac18de92e2d0da2c</t>
+          <t>https://www.indeed.com/viewjob?jk=f8293723295138e5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>Senior AWS Engineer - ML</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d784ad2795e0379d</t>
+          <t>https://www.indeed.com/viewjob?jk=e808d31f6fa032cf</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tunnl</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, RDS, Scala, DynamoDB, Splunk</t>
+          <t>AWS, Glue, Redshift, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b66532c29a2d2fb3</t>
+          <t>https://www.indeed.com/viewjob?jk=ac18de92e2d0da2c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior ETL Developer (Azure &amp; MDM/Reltio Focus)</t>
+          <t>Senior Engineer - Data</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Duncan, SC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bde84b2e0c4d7b5</t>
+          <t>https://www.indeed.com/viewjob?jk=d784ad2795e0379d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Information Technology - BI Developer</t>
+          <t>Senior ETL Developer (Azure &amp; MDM/Reltio Focus)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TCC Verizon Authorized Retailer</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fishers, IN, US USA</t>
+          <t>Duncan, SC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad7533e66ad7d7d8</t>
+          <t>https://www.indeed.com/viewjob?jk=6bde84b2e0c4d7b5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Developer I - Data Engineer</t>
+          <t>Information Technology - BI Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>TCC Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fishers, IN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, Kafka, Polars, Snowflake, Star Schema, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4e3803b26dd25a2</t>
+          <t>https://www.indeed.com/viewjob?jk=ad7533e66ad7d7d8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer, Security &amp; Information Technology - USDS</t>
+          <t>Senior Developer I - Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Azure, Spark, Scala, Kafka, Polars, Snowflake, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8131bdacb963c45</t>
+          <t>https://www.indeed.com/viewjob?jk=b4e3803b26dd25a2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Automation Architect – AI, Cloud &amp; Quality Engineering</t>
+          <t>Full Stack Software Engineer, Security &amp; Information Technology - USDS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BridgeNexus Technologies Inc</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, SQS, Azure, Scala, PostgreSQL, MongoDB, DynamoDB, CI/CD</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8019de144986634a</t>
+          <t>https://www.indeed.com/viewjob?jk=b8131bdacb963c45</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Automation Platform Engineer</t>
+          <t>Automation Architect – AI, Cloud &amp; Quality Engineering</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>BridgeNexus Technologies Inc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Littleton, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, AWS CodePipeline, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, SQS, Azure, Scala, PostgreSQL, MongoDB, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc94922007c35c18</t>
+          <t>https://www.indeed.com/viewjob?jk=8019de144986634a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Automation Platform Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ICAT Logistics, Inc.</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, AWS CodePipeline, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=490396287ca9423d</t>
+          <t>https://www.indeed.com/viewjob?jk=bc94922007c35c18</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ICAT Logistics, Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eba11dc550c0d956</t>
+          <t>https://www.indeed.com/viewjob?jk=490396287ca9423d</t>
         </is>
       </c>
     </row>
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Bambee</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>Redshift, ECS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=336bfe0af38918a1</t>
+          <t>https://www.indeed.com/viewjob?jk=3e3ad167874c8532</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Modem Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SIGNITIVES</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,87 +1291,87 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afef76c3c4cb302e</t>
+          <t>https://www.indeed.com/viewjob?jk=63cf613962496b27</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bambee</t>
+          <t>ICAT Logistics, Inc.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Redshift, ECS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Redshift, RDS, Azure, Data Lake Storage, GCP, BigQuery, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e3ad167874c8532</t>
+          <t>https://www.indeed.com/viewjob?jk=7dfde2e65a7bc1cc</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Modem Machine Learning Engineer</t>
+          <t>Data Engineer - Data Services</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Crown Equipment</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New Bremen, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63cf613962496b27</t>
+          <t>https://www.indeed.com/viewjob?jk=426a2df1dcd32427</t>
         </is>
       </c>
     </row>
@@ -1383,12 +1383,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ICAT Logistics, Inc.</t>
+          <t>Rediantt</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Lake Storage, GCP, BigQuery, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dfde2e65a7bc1cc</t>
+          <t>https://www.indeed.com/viewjob?jk=60d3683730583b9c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Services</t>
+          <t>Associate Data Engineer (REMOTE)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Crown Equipment</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New Bremen, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=426a2df1dcd32427</t>
+          <t>https://www.indeed.com/viewjob?jk=f62c64972906caa0</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Data Engineer (REMOTE)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Rediantt</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d3683730583b9c</t>
+          <t>https://www.indeed.com/viewjob?jk=ad092c66101d7698</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Associate Data Engineer (REMOTE)</t>
+          <t>Sr. Data Engineer - Cloud &amp; AI Platform [On-Site]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, RDS, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f62c64972906caa0</t>
+          <t>https://www.indeed.com/viewjob?jk=f7ba4a006c4d066d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Associate Data Engineer (REMOTE)</t>
+          <t>Data Engineer, Data Engineering and Analytics - USDS</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Hadoop, HDFS, Hive, Flume, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad092c66101d7698</t>
+          <t>https://www.indeed.com/viewjob?jk=5b155ae7711afa6e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Cloud &amp; AI Platform [On-Site]</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Darkk Alpha Capital</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7ba4a006c4d066d</t>
+          <t>https://www.indeed.com/viewjob?jk=f68d653a407d3790</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Engineering and Analytics - USDS</t>
+          <t>AI Engineering Intern</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Harvard Services Group, Inc</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Hadoop, HDFS, Hive, Flume, Spark, Scala, Kafka</t>
+          <t>Redshift, ECS, RDS, BigQuery, Snowflake, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b155ae7711afa6e</t>
+          <t>https://www.indeed.com/viewjob?jk=9a6b9d95984b1f2d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineering Intern</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Darkk Alpha Capital</t>
+          <t>Harvard Maintenance, Inc.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,87 +1641,87 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, PostgreSQL, ETL</t>
+          <t>Redshift, ECS, RDS, BigQuery, Snowflake, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f68d653a407d3790</t>
+          <t>https://www.indeed.com/viewjob?jk=780346cd358075a8</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI Engineering Intern</t>
+          <t>Cloud Software Engineer - Database</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Harvard Services Group, Inc</t>
+          <t>TP-LINK</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Redshift, ECS, RDS, BigQuery, Snowflake, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
+          <t>AWS, IAM, RDS, Cloud Storage, Scala, Kafka, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a6b9d95984b1f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=b4b22f5ed4795cb1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI Engineering Intern</t>
+          <t>Senior DATA Engineer with Healthcare background</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Harvard Maintenance, Inc.</t>
+          <t>Global KTech</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Redshift, ECS, RDS, BigQuery, Snowflake, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780346cd358075a8</t>
+          <t>https://www.indeed.com/viewjob?jk=23db276cee90e934</t>
         </is>
       </c>
     </row>
@@ -1833,17 +1833,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Engineering and Analytics - USDS</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Wilson Elser</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Hadoop, HDFS, Hive, Flume, Spark, Scala, Kafka</t>
+          <t>S3, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72ef2291619fe5e</t>
+          <t>https://www.indeed.com/viewjob?jk=798275d9488660df</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack Developer</t>
+          <t>Data Engineer, Data Engineering and Analytics - USDS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Benda Infotech</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, RDS, Hadoop, HDFS, Hive, Flume, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c284602b40afa505</t>
+          <t>https://www.indeed.com/viewjob?jk=d72ef2291619fe5e</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>AWS Platform Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Verification Technologies LLC</t>
+          <t>Synergy BIS</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Henderson, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, Timestream, Step Functions, S3, SQS, API Gateway, IAM, RDS</t>
+          <t>AWS, ECS, RDS, PostgreSQL, MySQL, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97a02535a97e1c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=dd743c87589a9510</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior BI Analyst</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Walker &amp; Dunlop</t>
+          <t>Verification Technologies LLC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Henderson, NV, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Lambda, Athena, Timestream, Step Functions, S3, SQS, API Gateway, IAM, RDS</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=827ebbc8cea913b8</t>
+          <t>https://www.indeed.com/viewjob?jk=97a02535a97e1c4c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer - Full Stack Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Point Wild</t>
+          <t>Benda Infotech</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e2022ce8366d457</t>
+          <t>https://www.indeed.com/viewjob?jk=c284602b40afa505</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71457be51c270627</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2022ce8366d457</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccc6509aa3c8ec42</t>
+          <t>https://www.indeed.com/viewjob?jk=71457be51c270627</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8f514785edf8fdc</t>
+          <t>https://www.indeed.com/viewjob?jk=ccc6509aa3c8ec42</t>
         </is>
       </c>
     </row>
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f99d76959b32539</t>
+          <t>https://www.indeed.com/viewjob?jk=d8f514785edf8fdc</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Analytical Engineer, Payment Data Intelligence - USDS</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Point Wild</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a567c2b339c20c2f</t>
+          <t>https://www.indeed.com/viewjob?jk=7f99d76959b32539</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Azure Databricks Platform Engineer</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>GRP Solutions</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Event Hubs, Medallion Architecture, Spark, PySpark, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=809ad06a2b50c327</t>
+          <t>https://www.indeed.com/viewjob?jk=cff7d97185671a3a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI ML Data Scientist</t>
+          <t>Data Analytical Engineer, Payment Data Intelligence - USDS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Westlake Village, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Azure, Hadoop, YARN, Spark, PySpark, Kafka, Oracle, NoSQL, Tableau, Docker</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce609bae5ee0d5a2</t>
+          <t>https://www.indeed.com/viewjob?jk=a567c2b339c20c2f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DevX / Developer Operations (Partner 16, Partner 18), ASG</t>
+          <t>Azure Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Andreessen Horowitz</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Event Hubs, Medallion Architecture, Spark, PySpark, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2570942407162c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=809ad06a2b50c327</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Site Reliability Engineer</t>
+          <t>AI ML Data Scientist</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Westlake Village, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
+          <t>Azure, Hadoop, YARN, Spark, PySpark, Kafka, Oracle, NoSQL, Tableau, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e4b910ec252456f</t>
+          <t>https://www.indeed.com/viewjob?jk=ce609bae5ee0d5a2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DevX / Developer Operations (Partner 16, Partner 18), ASG</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>a16z</t>
+          <t>Success Academy Charter Schools</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,17 +2341,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, MLOps, MLflow, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0f26d4983647c6b</t>
+          <t>https://www.indeed.com/viewjob?jk=fe5b87ce57fff653</t>
         </is>
       </c>
     </row>
@@ -2393,25 +2393,25 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>DevX / Developer Operations (Partner 16, Partner 18), ASG</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Vytl Controls Group</t>
+          <t>Andreessen Horowitz</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f97f2d7c736b559</t>
+          <t>https://www.indeed.com/viewjob?jk=2570942407162c4a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Informatica ETL Developer - 6326296</t>
+          <t>Software Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, Git</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1a17c04578e9be3</t>
+          <t>https://www.indeed.com/viewjob?jk=8e4b910ec252456f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Informatica ETL Developer - 6326296</t>
+          <t>DevX / Developer Operations (Partner 16, Partner 18), ASG</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>a16z</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21eab84e17f0b1ac</t>
+          <t>https://www.indeed.com/viewjob?jk=e0f26d4983647c6b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer III</t>
+          <t>EY-Parthenon - Strategy and Execution - Growth Platforms - Data Scientist - Sr Associate/Consultant</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, MLflow, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b58a2b9f1b9c3a51</t>
+          <t>https://www.indeed.com/viewjob?jk=06f1573e4d5b380e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Privacy &amp; Infrastructure - USDS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>MFour Mobile Research, Inc.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, HDFS, Hive, Spark, Kafka, MySQL, NoSQL, Kubernetes</t>
+          <t>AWS, RDS, Databricks, GCP, Spark, Scala, Kafka, Snowflake, dbt, Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=625f5552fcee590f</t>
+          <t>https://www.indeed.com/viewjob?jk=fde4359b0781ac36</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>Vytl Controls Group</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, SQS, API Gateway, ECS, RDS, Jenkins</t>
+          <t>RDS, Azure, Databricks, Scala, SQL Server, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e888182752c6207b</t>
+          <t>https://www.indeed.com/viewjob?jk=2f97f2d7c736b559</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Machine Learning Engineer III</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ERP SAVVY LLC</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Skillman, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Oozie, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, MLflow, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a04b59dd3c9c139</t>
+          <t>https://www.indeed.com/viewjob?jk=b58a2b9f1b9c3a51</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Digital Native Business</t>
+          <t>Software Engineer, Data Privacy &amp; Infrastructure - USDS</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, IAM, RDS, HDFS, Hive, Spark, Kafka, MySQL, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dec276bec6c38a67</t>
+          <t>https://www.indeed.com/viewjob?jk=625f5552fcee590f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Digital Native Business</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, SQS, API Gateway, ECS, RDS, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377873b4a91a42db</t>
+          <t>https://www.indeed.com/viewjob?jk=e888182752c6207b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer - AI Forward Engineer</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CarParts.com</t>
+          <t>ERP SAVVY LLC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Skillman, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
+          <t>Hadoop, HDFS, Oozie, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81e7e89cef9a97da</t>
+          <t>https://www.indeed.com/viewjob?jk=8a04b59dd3c9c139</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Platform Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Troon</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1849a5b7a2f2af9b</t>
+          <t>https://www.indeed.com/viewjob?jk=d00826f43274ea34</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Java Developer (Connected Services)</t>
+          <t>Resident Solutions Architect - Digital Native Business</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa3dcc861e4ac768</t>
+          <t>https://www.indeed.com/viewjob?jk=dec276bec6c38a67</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Resident Solutions Architect - Digital Native Business</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=936e44ddac734d7b</t>
+          <t>https://www.indeed.com/viewjob?jk=377873b4a91a42db</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer, Application Development</t>
+          <t>Sr. Full Stack Engineer - AI Forward Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CarParts.com</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e58bc4277f70431</t>
+          <t>https://www.indeed.com/viewjob?jk=81e7e89cef9a97da</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer, Application Development</t>
+          <t>Java Developer (Connected Services)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fea29a3880a03255</t>
+          <t>https://www.indeed.com/viewjob?jk=fa3dcc861e4ac768</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer, Application Development</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb3cb19cae9db9b</t>
+          <t>https://www.indeed.com/viewjob?jk=936e44ddac734d7b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer Fish Data Systems</t>
+          <t>Full Stack Senior Engineer, Application Development</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PACIFIC STATES MARINE FISHERIES COMMISSION</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Oracle, SQL Server, PostgreSQL, ELT, Power BI, CI/CD, Docker</t>
+          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b90c3fac511dfb2</t>
+          <t>https://www.indeed.com/viewjob?jk=4e58bc4277f70431</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Full Stack Cloud Engineer</t>
+          <t>Full Stack Senior Engineer, Application Development</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>The Akanksha LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaf16acc114cd913</t>
+          <t>https://www.indeed.com/viewjob?jk=fea29a3880a03255</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Full Stack Senior Engineer, Application Development</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=226e96da47ff2b1a</t>
+          <t>https://www.indeed.com/viewjob?jk=3bb3cb19cae9db9b</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Consultant – Data Engineer &amp; Governance</t>
+          <t>Full Stack Software Engineer Fish Data Systems</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Quisitive</t>
+          <t>PACIFIC STATES MARINE FISHERIES COMMISSION</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Data Factory, Oracle, SQL Server, PostgreSQL, ELT, Power BI, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd77d29cb01573c</t>
+          <t>https://www.indeed.com/viewjob?jk=0b90c3fac511dfb2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer â€“ Python/AI</t>
+          <t>Manufacturing Data Systems Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Ion Storage Systems</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Beltsville, MD, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
+          <t>RDS, Azure, Dataflow, Scala, ETL, ELT, Power BI, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb44a4b768419ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=2cfacddbdda92507</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer - Finance Modernization</t>
+          <t>Data Engineer (Remote - United States)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Nextech Systems</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Spark, Scala, CI/CD, Terraform, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, SQL Server, ELT, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ee917ec6e025e8</t>
+          <t>https://www.indeed.com/viewjob?jk=c0a946d2db71d280</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Engineer III, Platform Engineering</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>endava</t>
+          <t>Omnicell</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Cranberry Township, PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Kubernetes, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163d2dba42ea7b46</t>
+          <t>https://www.indeed.com/viewjob?jk=f0ef9b73a4ad4b77</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Salesforce Technical Architect, Data &amp; AI</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NeuraFlash, Part of Accenture</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Redshift, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Git</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3420dddc661e222d</t>
+          <t>https://www.indeed.com/viewjob?jk=226e96da47ff2b1a</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior DevOps/MLOps Engineer</t>
+          <t>Senior Data Consultant – Data Engineer &amp; Governance</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Algorized</t>
+          <t>Quisitive</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Campbell, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c88a8d02f220104</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd77d29cb01573c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Specialist - Quality Engineering</t>
+          <t>Data Engineer III (Platform)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>MAPFRE Insurance</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Webster, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, Scala, Data Modeling, ETL, CI/CD, Jenkins, Jenkins, Airflow, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53ced3da28996aca</t>
+          <t>https://www.indeed.com/viewjob?jk=1c94972b0ddefdba</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Model Risk Management</t>
+          <t>Software Engineer - Finance Modernization</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Vertex AI, Snowflake, ETL, MLflow, pytest, Git</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Spark, Scala, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4b8c7a56e0e088</t>
+          <t>https://www.indeed.com/viewjob?jk=15ee917ec6e025e8</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AI LLM Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Siemens Healthineers</t>
+          <t>endava</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, Data Modeling, ELT, Power BI, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77cc10c4736bb6e5</t>
+          <t>https://www.indeed.com/viewjob?jk=163d2dba42ea7b46</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Lakebase Sales Specialist- Financial Services</t>
+          <t>Salesforce Technical Architect, Data &amp; AI</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>NeuraFlash, Part of Accenture</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+          <t>AWS, Redshift, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d86224c98360290</t>
+          <t>https://www.indeed.com/viewjob?jk=3420dddc661e222d</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SAS Developer (with Admin Background)</t>
+          <t>Sr. Eng Software App Eng</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Unisys</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, ETL, CI/CD, Git</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Kafka, Oracle, SQL Server, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f708bb2089c8e37e</t>
+          <t>https://www.indeed.com/viewjob?jk=8c0ca1df0e1e155a</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SAS Developer (with Admin Background)</t>
+          <t>Senior DevOps/MLOps Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Algorized</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Campbell, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, ETL, CI/CD, Git</t>
+          <t>AWS, S3, ECS, IAM, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b030dd9a627fd2c</t>
+          <t>https://www.indeed.com/viewjob?jk=0c88a8d02f220104</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Specialist - Quality Engineering</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Azure, Medallion Architecture, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8d59fd93890be9a</t>
+          <t>https://www.indeed.com/viewjob?jk=53ced3da28996aca</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer - Analytics</t>
+          <t>SAS Developer (with Admin Background)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>EvergreenHealth</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, Star Schema, ETL, Power BI, Tableau, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=847c2fe533f1ec86</t>
+          <t>https://www.indeed.com/viewjob?jk=f708bb2089c8e37e</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (React/Typescript)</t>
+          <t>SAS Developer (with Admin Background)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Vertafore</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=757afec97d5d27e0</t>
+          <t>https://www.indeed.com/viewjob?jk=2b030dd9a627fd2c</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer - Java - Loops</t>
+          <t>Business Intelligence Developer - Analytics</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Copperleaf Technologies Inc.</t>
+          <t>EvergreenHealth</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Git, Datadog</t>
+          <t>RDS, Azure, Scala, Data Modeling, Star Schema, ETL, Power BI, Tableau, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe4ff78e6fcedc19</t>
+          <t>https://www.indeed.com/viewjob?jk=847c2fe533f1ec86</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Software Engineer (React/Typescript)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Vertafore</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Splunk, CI/CD, Kubernetes, Git</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d604ebca572d9a0d</t>
+          <t>https://www.indeed.com/viewjob?jk=757afec97d5d27e0</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Machine Learning Engineer, Model Risk Management</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Splunk, CI/CD, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, GCP, Vertex AI, Snowflake, ETL, MLflow, pytest, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=244f96a693bca9f8</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4b8c7a56e0e088</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI LLM Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Siemens Healthineers</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,15 +3706,190 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, Data Modeling, ELT, Power BI, Git, Python</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=77cc10c4736bb6e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Lakebase Sales Specialist- Financial Services</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d86224c98360290</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Data Engineer - Java - Loops</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Copperleaf Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe4ff78e6fcedc19</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
           <t>RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Splunk, CI/CD, Kubernetes, Git</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d604ebca572d9a0d</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>West Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Splunk, CI/CD, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=244f96a693bca9f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Splunk, CI/CD, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4229f7f9f0a4e0f7</t>
         </is>

--- a/results/job_matches_2026-06-04.xlsx
+++ b/results/job_matches_2026-06-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,60 +678,60 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. AWS Data Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>DevIQ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Hadoop</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d62532bd79c16947</t>
+          <t>https://www.indeed.com/viewjob?jk=f8293723295138e5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
+          <t>Senior AWS Engineer - ML</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9f4e94883170da4</t>
+          <t>https://www.indeed.com/viewjob?jk=e808d31f6fa032cf</t>
         </is>
       </c>
     </row>
@@ -762,38 +762,38 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feaf489696c6ebd7</t>
+          <t>https://www.indeed.com/viewjob?jk=6bde84b2e0c4d7b5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Information Technology - BI Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DevIQ</t>
+          <t>TCC Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Fishers, IN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8293723295138e5</t>
+          <t>https://www.indeed.com/viewjob?jk=ad7533e66ad7d7d8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior AWS Engineer - ML</t>
+          <t>Senior Developer I - Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
+          <t>AWS, Azure, Spark, Scala, Kafka, Polars, Snowflake, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,242 +846,242 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e808d31f6fa032cf</t>
+          <t>https://www.indeed.com/viewjob?jk=b4e3803b26dd25a2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Automation Architect – AI, Cloud &amp; Quality Engineering</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BridgeNexus Technologies Inc</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, SQS, Azure, Scala, PostgreSQL, MongoDB, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac18de92e2d0da2c</t>
+          <t>https://www.indeed.com/viewjob?jk=8019de144986634a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>Oracle HCM Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Lavisee Technologies</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d784ad2795e0379d</t>
+          <t>https://www.indeed.com/viewjob?jk=cac70b1298ea5c9e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior ETL Developer (Azure &amp; MDM/Reltio Focus)</t>
+          <t>Senior Automation Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Duncan, SC, US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, AWS CodePipeline, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bde84b2e0c4d7b5</t>
+          <t>https://www.indeed.com/viewjob?jk=bc94922007c35c18</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Information Technology - BI Developer</t>
+          <t>Python Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TCC Verizon Authorized Retailer</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Fishers, IN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, S3, Azure, GCP, Hadoop, HDFS, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad7533e66ad7d7d8</t>
+          <t>https://www.indeed.com/viewjob?jk=da84632d9568dfce</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Developer I - Data Engineer</t>
+          <t>Senior AWS Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>Teachers Retirement System</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, Kafka, Polars, Snowflake, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4e3803b26dd25a2</t>
+          <t>https://www.indeed.com/viewjob?jk=fdb97cb6b9e8a913</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer, Security &amp; Information Technology - USDS</t>
+          <t>Senior Data Engineer-Onsite</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Time Travel, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8131bdacb963c45</t>
+          <t>https://www.indeed.com/viewjob?jk=79f877445f165bc2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Automation Architect – AI, Cloud &amp; Quality Engineering</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BridgeNexus Technologies Inc</t>
+          <t>Bambee</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, SQS, Azure, Scala, PostgreSQL, MongoDB, DynamoDB, CI/CD</t>
+          <t>Redshift, ECS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,207 +1091,207 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8019de144986634a</t>
+          <t>https://www.indeed.com/viewjob?jk=3e3ad167874c8532</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Automation Platform Engineer</t>
+          <t>Modem Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Littleton, CO, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, AWS CodePipeline, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc94922007c35c18</t>
+          <t>https://www.indeed.com/viewjob?jk=63cf613962496b27</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ICAT Logistics, Inc.</t>
+          <t>clickhouse</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=490396287ca9423d</t>
+          <t>https://www.indeed.com/viewjob?jk=a0162d13045a3367</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Python Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>ICAT Logistics, Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Hadoop, HDFS, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Lake Storage, GCP, BigQuery, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da84632d9568dfce</t>
+          <t>https://www.indeed.com/viewjob?jk=7dfde2e65a7bc1cc</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior AWS Engineer</t>
+          <t>Data Engineer - Data Services</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Teachers Retirement System</t>
+          <t>Crown Equipment</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>New Bremen, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdb97cb6b9e8a913</t>
+          <t>https://www.indeed.com/viewjob?jk=426a2df1dcd32427</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bambee</t>
+          <t>Rediantt</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Redshift, ECS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e3ad167874c8532</t>
+          <t>https://www.indeed.com/viewjob?jk=60d3683730583b9c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Modem Machine Learning Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Darkk Alpha Capital</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63cf613962496b27</t>
+          <t>https://www.indeed.com/viewjob?jk=f68d653a407d3790</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Engineering Intern</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ICAT Logistics, Inc.</t>
+          <t>Harvard Services Group, Inc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Lake Storage, GCP, BigQuery, Scala, Snowflake, PostgreSQL</t>
+          <t>Redshift, ECS, RDS, BigQuery, Snowflake, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dfde2e65a7bc1cc</t>
+          <t>https://www.indeed.com/viewjob?jk=9a6b9d95984b1f2d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Services</t>
+          <t>AI Engineering Intern</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Crown Equipment</t>
+          <t>Harvard Maintenance, Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New Bremen, OH, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD</t>
+          <t>Redshift, ECS, RDS, BigQuery, Snowflake, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,54 +1371,54 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=426a2df1dcd32427</t>
+          <t>https://www.indeed.com/viewjob?jk=780346cd358075a8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Software Engineer - Database</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Rediantt</t>
+          <t>TP-LINK</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, IAM, RDS, Cloud Storage, Scala, Kafka, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d3683730583b9c</t>
+          <t>https://www.indeed.com/viewjob?jk=b4b22f5ed4795cb1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Associate Data Engineer (REMOTE)</t>
+          <t>Senior DATA Engineer with Healthcare background</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Global KTech</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1427,81 +1427,81 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f62c64972906caa0</t>
+          <t>https://www.indeed.com/viewjob?jk=23db276cee90e934</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Associate Data Engineer (REMOTE)</t>
+          <t>Senior Cloud Software Engineer - Database</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>TP-LINK</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Cloud Storage, Scala, Kafka, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad092c66101d7698</t>
+          <t>https://www.indeed.com/viewjob?jk=c97fb5b4fe767905</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Cloud &amp; AI Platform [On-Site]</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,54 +1511,54 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7ba4a006c4d066d</t>
+          <t>https://www.indeed.com/viewjob?jk=424fe727a6834d5b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Engineering and Analytics - USDS</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Wilson Elser</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Hadoop, HDFS, Hive, Flume, Spark, Scala, Kafka</t>
+          <t>S3, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b155ae7711afa6e</t>
+          <t>https://www.indeed.com/viewjob?jk=798275d9488660df</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Platform Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Darkk Alpha Capital</t>
+          <t>Synergy BIS</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1567,11 +1567,11 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, PostgreSQL, ETL</t>
+          <t>AWS, ECS, RDS, PostgreSQL, MySQL, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f68d653a407d3790</t>
+          <t>https://www.indeed.com/viewjob?jk=dd743c87589a9510</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Engineering Intern</t>
+          <t>Software Engineer - Full Stack Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Harvard Services Group, Inc</t>
+          <t>Benda Infotech</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Redshift, ECS, RDS, BigQuery, Snowflake, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a6b9d95984b1f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=c284602b40afa505</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI Engineering Intern</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Harvard Maintenance, Inc.</t>
+          <t>Verification Technologies LLC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Henderson, NV, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Redshift, ECS, RDS, BigQuery, Snowflake, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
+          <t>AWS, Lambda, Athena, Timestream, Step Functions, S3, SQS, API Gateway, IAM, RDS</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780346cd358075a8</t>
+          <t>https://www.indeed.com/viewjob?jk=97a02535a97e1c4c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer - Database</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TP-LINK</t>
+          <t>Point Wild</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,29 +1676,29 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Cloud Storage, Scala, Kafka, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4b22f5ed4795cb1</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2022ce8366d457</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior DATA Engineer with Healthcare background</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Global KTech</t>
+          <t>Point Wild</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23db276cee90e934</t>
+          <t>https://www.indeed.com/viewjob?jk=71457be51c270627</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer - Database</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TP-LINK</t>
+          <t>Point Wild</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Cloud Storage, Scala, Kafka, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c97fb5b4fe767905</t>
+          <t>https://www.indeed.com/viewjob?jk=ccc6509aa3c8ec42</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>Point Wild</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424fe727a6834d5b</t>
+          <t>https://www.indeed.com/viewjob?jk=d8f514785edf8fdc</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Point Wild</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Event Hubs, Snowflake, PostgreSQL, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5cff3964beedb24</t>
+          <t>https://www.indeed.com/viewjob?jk=7f99d76959b32539</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Tech Debt / Refresh Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Wilson Elser</t>
+          <t>Concept Plus</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>S3, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,67 +1861,67 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=798275d9488660df</t>
+          <t>https://www.indeed.com/viewjob?jk=c7cd058ee0887b50</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Engineering and Analytics - USDS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Hadoop, HDFS, Hive, Flume, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72ef2291619fe5e</t>
+          <t>https://www.indeed.com/viewjob?jk=bd033c06ef261546</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AWS Platform Architect</t>
+          <t>Data Engineer II - QuantumBlack, AI by McKinsey</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Synergy BIS</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, PostgreSQL, MySQL, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, dbt, MLOps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd743c87589a9510</t>
+          <t>https://www.indeed.com/viewjob?jk=ad0333886fec2326</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Verification Technologies LLC</t>
+          <t>GRP Solutions</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Henderson, NV, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, Timestream, Step Functions, S3, SQS, API Gateway, IAM, RDS</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97a02535a97e1c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=cff7d97185671a3a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack Developer</t>
+          <t>AI ML Data Scientist</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Benda Infotech</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Westlake Village, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps</t>
+          <t>Azure, Hadoop, YARN, Spark, PySpark, Kafka, Oracle, NoSQL, Tableau, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,42 +2001,42 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c284602b40afa505</t>
+          <t>https://www.indeed.com/viewjob?jk=ce609bae5ee0d5a2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Point Wild</t>
+          <t>Success Academy Charter Schools</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, MLOps, MLflow, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e2022ce8366d457</t>
+          <t>https://www.indeed.com/viewjob?jk=fe5b87ce57fff653</t>
         </is>
       </c>
     </row>
@@ -2048,55 +2048,55 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Point Wild</t>
+          <t>Demand Works Media LLC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71457be51c270627</t>
+          <t>https://www.indeed.com/viewjob?jk=26540d1cf37e6176</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineering SMTS</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Point Wild</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Scala, ELT, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccc6509aa3c8ec42</t>
+          <t>https://www.indeed.com/viewjob?jk=bce752ad6855e523</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>DevX / Developer Operations (Partner 16, Partner 18), ASG</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Point Wild</t>
+          <t>Andreessen Horowitz</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8f514785edf8fdc</t>
+          <t>https://www.indeed.com/viewjob?jk=2570942407162c4a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Point Wild</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f99d76959b32539</t>
+          <t>https://www.indeed.com/viewjob?jk=8e4b910ec252456f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>DevX / Developer Operations (Partner 16, Partner 18), ASG</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>GRP Solutions</t>
+          <t>a16z</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,314 +2201,314 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cff7d97185671a3a</t>
+          <t>https://www.indeed.com/viewjob?jk=e0f26d4983647c6b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Analytical Engineer, Payment Data Intelligence - USDS</t>
+          <t>Senior Data Engineer I - QuantumBlack, AI by McKinsey</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Dask, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a567c2b339c20c2f</t>
+          <t>https://www.indeed.com/viewjob?jk=4da87067b7b52c98</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Azure Databricks Platform Engineer</t>
+          <t>EY-Parthenon - Strategy and Execution - Growth Platforms - Data Scientist - Sr Associate/Consultant</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Event Hubs, Medallion Architecture, Spark, PySpark, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=809ad06a2b50c327</t>
+          <t>https://www.indeed.com/viewjob?jk=06f1573e4d5b380e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AI ML Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>MFour Mobile Research, Inc.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Westlake Village, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Azure, Hadoop, YARN, Spark, PySpark, Kafka, Oracle, NoSQL, Tableau, Docker</t>
+          <t>AWS, RDS, Databricks, GCP, Spark, Scala, Kafka, Snowflake, dbt, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce609bae5ee0d5a2</t>
+          <t>https://www.indeed.com/viewjob?jk=fde4359b0781ac36</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Machine Learning Engineer III</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Success Academy Charter Schools</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, MLOps, MLflow, Airflow, Git, Python</t>
+          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, MLflow, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe5b87ce57fff653</t>
+          <t>https://www.indeed.com/viewjob?jk=b58a2b9f1b9c3a51</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>ERP SAVVY LLC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Skillman, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, ELT, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>Hadoop, HDFS, Oozie, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bce752ad6855e523</t>
+          <t>https://www.indeed.com/viewjob?jk=8a04b59dd3c9c139</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DevX / Developer Operations (Partner 16, Partner 18), ASG</t>
+          <t>Senior Data Platform Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Andreessen Horowitz</t>
+          <t>Troon</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2570942407162c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=d00826f43274ea34</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Site Reliability Engineer</t>
+          <t>Resident Solutions Architect - Digital Native Business</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e4b910ec252456f</t>
+          <t>https://www.indeed.com/viewjob?jk=dec276bec6c38a67</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DevX / Developer Operations (Partner 16, Partner 18), ASG</t>
+          <t>Resident Solutions Architect - Digital Native Business</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>a16z</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0f26d4983647c6b</t>
+          <t>https://www.indeed.com/viewjob?jk=377873b4a91a42db</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>EY-Parthenon - Strategy and Execution - Growth Platforms - Data Scientist - Sr Associate/Consultant</t>
+          <t>Sr. Full Stack Engineer - AI Forward Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>CarParts.com</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f1573e4d5b380e</t>
+          <t>https://www.indeed.com/viewjob?jk=81e7e89cef9a97da</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Developer (Connected Services)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MFour Mobile Research, Inc.</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Spark, Scala, Kafka, Snowflake, dbt, Airflow</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde4359b0781ac36</t>
+          <t>https://www.indeed.com/viewjob?jk=fa3dcc861e4ac768</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Vytl Controls Group</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f97f2d7c736b559</t>
+          <t>https://www.indeed.com/viewjob?jk=936e44ddac734d7b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer III</t>
+          <t>Full Stack Senior Engineer, Application Development</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, MLflow, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b58a2b9f1b9c3a51</t>
+          <t>https://www.indeed.com/viewjob?jk=4e58bc4277f70431</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Privacy &amp; Infrastructure - USDS</t>
+          <t>Full Stack Senior Engineer, Application Development</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, HDFS, Hive, Spark, Kafka, MySQL, NoSQL, Kubernetes</t>
+          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=625f5552fcee590f</t>
+          <t>https://www.indeed.com/viewjob?jk=fea29a3880a03255</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Full Stack Senior Engineer, Application Development</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, SQS, API Gateway, ECS, RDS, Jenkins</t>
+          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e888182752c6207b</t>
+          <t>https://www.indeed.com/viewjob?jk=3bb3cb19cae9db9b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Full Stack Software Engineer Fish Data Systems</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ERP SAVVY LLC</t>
+          <t>PACIFIC STATES MARINE FISHERIES COMMISSION</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Skillman, NJ, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,42 +2726,42 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Oozie, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Azure, Data Factory, Oracle, SQL Server, PostgreSQL, ELT, Power BI, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a04b59dd3c9c139</t>
+          <t>https://www.indeed.com/viewjob?jk=0b90c3fac511dfb2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Platform Architect</t>
+          <t>Application Engineer IV</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Troon</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Dataflow, Spark, PySpark, Scala, MongoDB</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d00826f43274ea34</t>
+          <t>https://www.indeed.com/viewjob?jk=b9da97f7358a9449</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Digital Native Business</t>
+          <t>Manufacturing Data Systems Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Ion Storage Systems</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Beltsville, MD, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Dataflow, Scala, ETL, ELT, Power BI, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dec276bec6c38a67</t>
+          <t>https://www.indeed.com/viewjob?jk=2cfacddbdda92507</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Digital Native Business</t>
+          <t>Data Engineer (Remote - United States)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Nextech Systems</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, SQL Server, ELT, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377873b4a91a42db</t>
+          <t>https://www.indeed.com/viewjob?jk=c0a946d2db71d280</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer - AI Forward Engineer</t>
+          <t>Engineer III, Platform Engineering</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CarParts.com</t>
+          <t>Omnicell</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Cranberry Township, PA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Kubernetes, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81e7e89cef9a97da</t>
+          <t>https://www.indeed.com/viewjob?jk=f0ef9b73a4ad4b77</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Java Developer (Connected Services)</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa3dcc861e4ac768</t>
+          <t>https://www.indeed.com/viewjob?jk=226e96da47ff2b1a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Consultant – Data Engineer &amp; Governance</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Quisitive</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,67 +2946,67 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=936e44ddac734d7b</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd77d29cb01573c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer, Application Development</t>
+          <t>Data Engineer III (Platform)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>MAPFRE Insurance</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Webster, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Glue, Scala, Data Modeling, ETL, CI/CD, Jenkins, Jenkins, Airflow, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e58bc4277f70431</t>
+          <t>https://www.indeed.com/viewjob?jk=1c94972b0ddefdba</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer, Application Development</t>
+          <t>Software Engineer - Finance Modernization</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Spark, Scala, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,94 +3016,94 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fea29a3880a03255</t>
+          <t>https://www.indeed.com/viewjob?jk=15ee917ec6e025e8</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer, Application Development</t>
+          <t>Sr. Programmer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>COMMUNITY BEHAVIORAL HEALTH</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb3cb19cae9db9b</t>
+          <t>https://www.indeed.com/viewjob?jk=93628dfc1ed2e57f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer Fish Data Systems</t>
+          <t>Lakebase Sales Specialist</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PACIFIC STATES MARINE FISHERIES COMMISSION</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Oracle, SQL Server, PostgreSQL, ELT, Power BI, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b90c3fac511dfb2</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9c11c9c5d79b69</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Manufacturing Data Systems Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ion Storage Systems</t>
+          <t>endava</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Beltsville, MD, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, ETL, ELT, Power BI, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,19 +3121,19 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cfacddbdda92507</t>
+          <t>https://www.indeed.com/viewjob?jk=163d2dba42ea7b46</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote - United States)</t>
+          <t>Salesforce Technical Architect, Data &amp; AI</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Nextech Systems</t>
+          <t>NeuraFlash, Part of Accenture</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, SQL Server, ELT, Terraform</t>
+          <t>AWS, Redshift, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0a946d2db71d280</t>
+          <t>https://www.indeed.com/viewjob?jk=3420dddc661e222d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Engineer III, Platform Engineering</t>
+          <t>Senior DevOps/MLOps Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Omnicell</t>
+          <t>Algorized</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cranberry Township, PA, US USA</t>
+          <t>Campbell, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Kubernetes, Git, CloudWatch</t>
+          <t>AWS, S3, ECS, IAM, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0ef9b73a4ad4b77</t>
+          <t>https://www.indeed.com/viewjob?jk=0c88a8d02f220104</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Senior Specialist - Quality Engineering</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=226e96da47ff2b1a</t>
+          <t>https://www.indeed.com/viewjob?jk=53ced3da28996aca</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Consultant – Data Engineer &amp; Governance</t>
+          <t>Senior Machine Learning Engineer, Model Risk Management</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Quisitive</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, GCP, Vertex AI, Snowflake, ETL, MLflow, pytest, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd77d29cb01573c</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4b8c7a56e0e088</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer III (Platform)</t>
+          <t>AI LLM Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MAPFRE Insurance</t>
+          <t>Siemens Healthineers</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Webster, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Glue, Scala, Data Modeling, ETL, CI/CD, Jenkins, Jenkins, Airflow, Git</t>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, Data Modeling, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c94972b0ddefdba</t>
+          <t>https://www.indeed.com/viewjob?jk=77cc10c4736bb6e5</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer - Finance Modernization</t>
+          <t>SAS Developer (with Admin Background)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Spark, Scala, CI/CD, Terraform, Git</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ee917ec6e025e8</t>
+          <t>https://www.indeed.com/viewjob?jk=f708bb2089c8e37e</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>SAS Developer (with Admin Background)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>endava</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163d2dba42ea7b46</t>
+          <t>https://www.indeed.com/viewjob?jk=2b030dd9a627fd2c</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Salesforce Technical Architect, Data &amp; AI</t>
+          <t>Business Intelligence Developer - Analytics</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>NeuraFlash, Part of Accenture</t>
+          <t>EvergreenHealth</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Redshift, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Git</t>
+          <t>RDS, Azure, Scala, Data Modeling, Star Schema, ETL, Power BI, Tableau, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3420dddc661e222d</t>
+          <t>https://www.indeed.com/viewjob?jk=847c2fe533f1ec86</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr. Eng Software App Eng</t>
+          <t>Sr. Software Engineer (React/Typescript)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Unisys</t>
+          <t>Vertafore</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Kafka, Oracle, SQL Server, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c0ca1df0e1e155a</t>
+          <t>https://www.indeed.com/viewjob?jk=757afec97d5d27e0</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior DevOps/MLOps Engineer</t>
+          <t>Data Engineer - Java - Loops</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Algorized</t>
+          <t>Copperleaf Technologies Inc.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Campbell, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,437 +3461,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Git, Datadog</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c88a8d02f220104</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Senior Specialist - Quality Engineering</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>LTIMindtree</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Splunk, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=53ced3da28996aca</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>SAS Developer (with Admin Background)</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f708bb2089c8e37e</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>SAS Developer (with Admin Background)</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2b030dd9a627fd2c</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer - Analytics</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>EvergreenHealth</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Kirkland, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Data Modeling, Star Schema, ETL, Power BI, Tableau, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=847c2fe533f1ec86</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer (React/Typescript)</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Vertafore</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=757afec97d5d27e0</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer, Model Risk Management</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Block</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, GCP, Vertex AI, Snowflake, ETL, MLflow, pytest, Git</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4b8c7a56e0e088</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>AI LLM Engineer</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Siemens Healthineers</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, Data Modeling, ELT, Power BI, Git, Python</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=77cc10c4736bb6e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Lakebase Sales Specialist- Financial Services</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6d86224c98360290</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Data Engineer - Java - Loops</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Copperleaf Technologies Inc.</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=fe4ff78e6fcedc19</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Splunk, CI/CD, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d604ebca572d9a0d</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>West Des Moines, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Splunk, CI/CD, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=244f96a693bca9f8</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Splunk, CI/CD, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4229f7f9f0a4e0f7</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-04.xlsx
+++ b/results/job_matches_2026-06-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,35 +468,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Expert / Data Lakehouse Consultant</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IKS Health</t>
+          <t>Bilink Corp</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>24.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f18524a0d1c2e02e</t>
+          <t>https://www.indeed.com/viewjob?jk=6ef7670a3dacf51f</t>
         </is>
       </c>
     </row>
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer III - Data Platform</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BONbLOC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, RDS, Google Cloud Platform, BigQuery, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Databricks, Unity Catalog, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,19 +566,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=203332422aec13ef</t>
+          <t>https://www.indeed.com/viewjob?jk=d2aebd4405215d87</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Applied Architect (.NET &amp; Databricks)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Symhas</t>
+          <t>BONbLOC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Glue, EMR, Redshift, S3, RDS, Google Cloud Platform, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3c1f686434a6c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=203332422aec13ef</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>AI Applied Architect (.NET &amp; Databricks)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Decision Foundry</t>
+          <t>Symhas</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, API Gateway, IAM, RDS, Azure</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4373bea89867ea0b</t>
+          <t>https://www.indeed.com/viewjob?jk=c3c1f686434a6c4c</t>
         </is>
       </c>
     </row>
@@ -678,25 +678,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DevIQ</t>
+          <t>Decision Foundry</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, API Gateway, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8293723295138e5</t>
+          <t>https://www.indeed.com/viewjob?jk=4373bea89867ea0b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AWS Engineer - ML</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>DevIQ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e808d31f6fa032cf</t>
+          <t>https://www.indeed.com/viewjob?jk=f8293723295138e5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior ETL Developer (Azure &amp; MDM/Reltio Focus)</t>
+          <t>Senior AWS Engineer - ML</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Duncan, SC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bde84b2e0c4d7b5</t>
+          <t>https://www.indeed.com/viewjob?jk=e808d31f6fa032cf</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Information Technology - BI Developer</t>
+          <t>Senior ETL Developer (Azure &amp; MDM/Reltio Focus)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TCC Verizon Authorized Retailer</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fishers, IN, US USA</t>
+          <t>Duncan, SC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad7533e66ad7d7d8</t>
+          <t>https://www.indeed.com/viewjob?jk=6bde84b2e0c4d7b5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Developer I - Data Engineer</t>
+          <t>Information Technology - BI Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>TCC Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fishers, IN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, Kafka, Polars, Snowflake, Star Schema, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4e3803b26dd25a2</t>
+          <t>https://www.indeed.com/viewjob?jk=ad7533e66ad7d7d8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Automation Architect – AI, Cloud &amp; Quality Engineering</t>
+          <t>Blockchain Java Backend Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BridgeNexus Technologies Inc</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, SQS, Azure, Scala, PostgreSQL, MongoDB, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8019de144986634a</t>
+          <t>https://www.indeed.com/viewjob?jk=d3b304f9c143a865</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Oracle HCM Developer</t>
+          <t>Automation Architect – AI, Cloud &amp; Quality Engineering</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lavisee Technologies</t>
+          <t>BridgeNexus Technologies Inc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Glue, Lambda, SQS, Azure, Scala, PostgreSQL, MongoDB, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cac70b1298ea5c9e</t>
+          <t>https://www.indeed.com/viewjob?jk=8019de144986634a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Automation Platform Engineer</t>
+          <t>Oracle HCM Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Lavisee Technologies</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Littleton, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,104 +941,104 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, AWS CodePipeline, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc94922007c35c18</t>
+          <t>https://www.indeed.com/viewjob?jk=cac70b1298ea5c9e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Python Data Engineer</t>
+          <t>Senior Automation Platform Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Hadoop, HDFS, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, AWS CodePipeline, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da84632d9568dfce</t>
+          <t>https://www.indeed.com/viewjob?jk=bc94922007c35c18</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior AWS Engineer</t>
+          <t>Python Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Teachers Retirement System</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
+          <t>AWS, S3, Azure, GCP, Hadoop, HDFS, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdb97cb6b9e8a913</t>
+          <t>https://www.indeed.com/viewjob?jk=da84632d9568dfce</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer-Onsite</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Bambee</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Time Travel, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>Redshift, ECS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79f877445f165bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=3e3ad167874c8532</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bambee</t>
+          <t>eHub</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Redshift, ECS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Dimensional Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e3ad167874c8532</t>
+          <t>https://www.indeed.com/viewjob?jk=a462b164d07d7ba9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Modem Machine Learning Engineer</t>
+          <t>Senior AWS Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Teachers Retirement System</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63cf613962496b27</t>
+          <t>https://www.indeed.com/viewjob?jk=fdb97cb6b9e8a913</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Engineer-Onsite</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>clickhouse</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Time Travel, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,59 +1161,59 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0162d13045a3367</t>
+          <t>https://www.indeed.com/viewjob?jk=79f877445f165bc2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Modem Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ICAT Logistics, Inc.</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Lake Storage, GCP, BigQuery, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dfde2e65a7bc1cc</t>
+          <t>https://www.indeed.com/viewjob?jk=63cf613962496b27</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Services</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Crown Equipment</t>
+          <t>Darkk Alpha Capital</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New Bremen, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=426a2df1dcd32427</t>
+          <t>https://www.indeed.com/viewjob?jk=f68d653a407d3790</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Engineering Intern</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rediantt</t>
+          <t>Harvard Services Group, Inc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>Redshift, ECS, RDS, BigQuery, Snowflake, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d3683730583b9c</t>
+          <t>https://www.indeed.com/viewjob?jk=9a6b9d95984b1f2d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineering Intern</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Darkk Alpha Capital</t>
+          <t>Harvard Maintenance, Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,104 +1291,104 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, PostgreSQL, ETL</t>
+          <t>Redshift, ECS, RDS, BigQuery, Snowflake, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f68d653a407d3790</t>
+          <t>https://www.indeed.com/viewjob?jk=780346cd358075a8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Engineering Intern</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Harvard Services Group, Inc</t>
+          <t>Wilson Elser</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Redshift, ECS, RDS, BigQuery, Snowflake, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
+          <t>S3, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a6b9d95984b1f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=798275d9488660df</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI Engineering Intern</t>
+          <t>Senior DATA Engineer with Healthcare background</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Harvard Maintenance, Inc.</t>
+          <t>Global KTech</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Redshift, ECS, RDS, BigQuery, Snowflake, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780346cd358075a8</t>
+          <t>https://www.indeed.com/viewjob?jk=23db276cee90e934</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer - Database</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TP-LINK</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Cloud Storage, Scala, Kafka, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4b22f5ed4795cb1</t>
+          <t>https://www.indeed.com/viewjob?jk=9e053efd9a837ce7</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior DATA Engineer with Healthcare background</t>
+          <t>Cloud Software Engineer - Database</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Global KTech</t>
+          <t>TP-LINK</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, IAM, RDS, Cloud Storage, Scala, Kafka, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23db276cee90e934</t>
+          <t>https://www.indeed.com/viewjob?jk=b4b22f5ed4795cb1</t>
         </is>
       </c>
     </row>
@@ -1518,17 +1518,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>AWS Platform Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Wilson Elser</t>
+          <t>Synergy BIS</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>S3, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, ECS, RDS, PostgreSQL, MySQL, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=798275d9488660df</t>
+          <t>https://www.indeed.com/viewjob?jk=dd743c87589a9510</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AWS Platform Architect</t>
+          <t>Tableau Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Synergy BIS</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, PostgreSQL, MySQL, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd743c87589a9510</t>
+          <t>https://www.indeed.com/viewjob?jk=5e7f11b8f38a8ecd</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Tech Debt / Refresh Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Verification Technologies LLC</t>
+          <t>Concept Plus</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Henderson, NV, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,112 +1641,112 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, Timestream, Step Functions, S3, SQS, API Gateway, IAM, RDS</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97a02535a97e1c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=c7cd058ee0887b50</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Point Wild</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e2022ce8366d457</t>
+          <t>https://www.indeed.com/viewjob?jk=bd033c06ef261546</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Point Wild</t>
+          <t>GRP Solutions</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71457be51c270627</t>
+          <t>https://www.indeed.com/viewjob?jk=cff7d97185671a3a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AI ML Data Scientist</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Point Wild</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westlake Village, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>Azure, Hadoop, YARN, Spark, PySpark, Kafka, Oracle, NoSQL, Tableau, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,102 +1756,102 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccc6509aa3c8ec42</t>
+          <t>https://www.indeed.com/viewjob?jk=ce609bae5ee0d5a2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer II - QuantumBlack, AI by McKinsey</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Point Wild</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, dbt, MLOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8f514785edf8fdc</t>
+          <t>https://www.indeed.com/viewjob?jk=ad0333886fec2326</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Point Wild</t>
+          <t>Success Academy Charter Schools</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, GCP, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, MLOps, MLflow, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f99d76959b32539</t>
+          <t>https://www.indeed.com/viewjob?jk=fe5b87ce57fff653</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Tech Debt / Refresh Engineer</t>
+          <t>Senior Software Development Engineer In Test, ML/AI</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Concept Plus</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7cd058ee0887b50</t>
+          <t>https://www.indeed.com/viewjob?jk=ea671c360a6a09f8</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>Demand Works Media LLC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd033c06ef261546</t>
+          <t>https://www.indeed.com/viewjob?jk=26540d1cf37e6176</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer II - QuantumBlack, AI by McKinsey</t>
+          <t>DevX / Developer Operations (Partner 16, Partner 18), ASG</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Andreessen Horowitz</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, dbt, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad0333886fec2326</t>
+          <t>https://www.indeed.com/viewjob?jk=2570942407162c4a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Software Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GRP Solutions</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,64 +1956,64 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cff7d97185671a3a</t>
+          <t>https://www.indeed.com/viewjob?jk=8e4b910ec252456f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI ML Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Paramount Global US Inc</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Westlake Village, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Azure, Hadoop, YARN, Spark, PySpark, Kafka, Oracle, NoSQL, Tableau, Docker</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce609bae5ee0d5a2</t>
+          <t>https://www.indeed.com/viewjob?jk=ce5b8ffd36870fad</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>EY-Parthenon - Strategy and Execution - Growth Platforms - Data Scientist - Sr Associate/Consultant</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Success Academy Charter Schools</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2022,11 +2022,11 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, MLOps, MLflow, Airflow, Git, Python</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe5b87ce57fff653</t>
+          <t>https://www.indeed.com/viewjob?jk=06f1573e4d5b380e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Engineer I - QuantumBlack, AI by McKinsey</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Demand Works Media LLC</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Dask, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,164 +2071,164 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26540d1cf37e6176</t>
+          <t>https://www.indeed.com/viewjob?jk=4da87067b7b52c98</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>MFour Mobile Research, Inc.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, ELT, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Databricks, GCP, Spark, Scala, Kafka, Snowflake, dbt, Airflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bce752ad6855e523</t>
+          <t>https://www.indeed.com/viewjob?jk=fde4359b0781ac36</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DevX / Developer Operations (Partner 16, Partner 18), ASG</t>
+          <t>Machine Learning Engineer III</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Andreessen Horowitz</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, MLflow, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2570942407162c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=b58a2b9f1b9c3a51</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Site Reliability Engineer</t>
+          <t>Senior Data Platform Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Troon</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e4b910ec252456f</t>
+          <t>https://www.indeed.com/viewjob?jk=d00826f43274ea34</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DevX / Developer Operations (Partner 16, Partner 18), ASG</t>
+          <t>Resident Solutions Architect - Digital Native Business</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>a16z</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0f26d4983647c6b</t>
+          <t>https://www.indeed.com/viewjob?jk=dec276bec6c38a67</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer I - QuantumBlack, AI by McKinsey</t>
+          <t>Resident Solutions Architect - Digital Native Business</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Dask, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4da87067b7b52c98</t>
+          <t>https://www.indeed.com/viewjob?jk=377873b4a91a42db</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>EY-Parthenon - Strategy and Execution - Growth Platforms - Data Scientist - Sr Associate/Consultant</t>
+          <t>Data Analyst — AI-Driven Insights</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f1573e4d5b380e</t>
+          <t>https://www.indeed.com/viewjob?jk=e573f908d6ce2f1d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Full Stack Engineer - AI Forward Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MFour Mobile Research, Inc.</t>
+          <t>CarParts.com</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Spark, Scala, Kafka, Snowflake, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde4359b0781ac36</t>
+          <t>https://www.indeed.com/viewjob?jk=81e7e89cef9a97da</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer III</t>
+          <t>Java Developer (Connected Services)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, MLflow, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b58a2b9f1b9c3a51</t>
+          <t>https://www.indeed.com/viewjob?jk=fa3dcc861e4ac768</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ERP SAVVY LLC</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Skillman, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Oozie, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, Power BI</t>
+          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a04b59dd3c9c139</t>
+          <t>https://www.indeed.com/viewjob?jk=936e44ddac734d7b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Platform Architect</t>
+          <t>Full Stack Senior Engineer, Application Development</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Troon</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d00826f43274ea34</t>
+          <t>https://www.indeed.com/viewjob?jk=4e58bc4277f70431</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Digital Native Business</t>
+          <t>Full Stack Senior Engineer, Application Development</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dec276bec6c38a67</t>
+          <t>https://www.indeed.com/viewjob?jk=fea29a3880a03255</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Digital Native Business</t>
+          <t>Full Stack Senior Engineer, Application Development</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377873b4a91a42db</t>
+          <t>https://www.indeed.com/viewjob?jk=3bb3cb19cae9db9b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer - AI Forward Engineer</t>
+          <t>Full Stack Software Engineer Fish Data Systems</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CarParts.com</t>
+          <t>PACIFIC STATES MARINE FISHERIES COMMISSION</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,64 +2516,64 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Oracle, SQL Server, PostgreSQL, ELT, Power BI, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81e7e89cef9a97da</t>
+          <t>https://www.indeed.com/viewjob?jk=0b90c3fac511dfb2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Java Developer (Connected Services)</t>
+          <t>Manufacturing Data Systems Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Ion Storage Systems</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Beltsville, MD, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Dataflow, Scala, ETL, ELT, Power BI, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa3dcc861e4ac768</t>
+          <t>https://www.indeed.com/viewjob?jk=2cfacddbdda92507</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer (Remote - United States)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Nextech Systems</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2582,46 +2582,46 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, SQL Server, ELT, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=936e44ddac734d7b</t>
+          <t>https://www.indeed.com/viewjob?jk=c0a946d2db71d280</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer, Application Development</t>
+          <t>Software Engineer - Finance Modernization</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Spark, Scala, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,102 +2631,102 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e58bc4277f70431</t>
+          <t>https://www.indeed.com/viewjob?jk=15ee917ec6e025e8</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer, Application Development</t>
+          <t>Application Engineer IV</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Dataflow, Spark, PySpark, Scala, MongoDB</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fea29a3880a03255</t>
+          <t>https://www.indeed.com/viewjob?jk=b9da97f7358a9449</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer, Application Development</t>
+          <t>Engineer III, Platform Engineering</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Omnicell</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Cranberry Township, PA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Kubernetes, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb3cb19cae9db9b</t>
+          <t>https://www.indeed.com/viewjob?jk=f0ef9b73a4ad4b77</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer Fish Data Systems</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PACIFIC STATES MARINE FISHERIES COMMISSION</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Oracle, SQL Server, PostgreSQL, ELT, Power BI, CI/CD, Docker</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b90c3fac511dfb2</t>
+          <t>https://www.indeed.com/viewjob?jk=226e96da47ff2b1a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Application Engineer IV</t>
+          <t>Data Engineer III (Platform)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MAPFRE Insurance</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Webster, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Dataflow, Spark, PySpark, Scala, MongoDB</t>
+          <t>AWS, Glue, Scala, Data Modeling, ETL, CI/CD, Jenkins, Jenkins, Airflow, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9da97f7358a9449</t>
+          <t>https://www.indeed.com/viewjob?jk=1c94972b0ddefdba</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Manufacturing Data Systems Engineer</t>
+          <t>Lakebase Sales Specialist</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ion Storage Systems</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Beltsville, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, ETL, ELT, Power BI, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cfacddbdda92507</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9c11c9c5d79b69</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote - United States)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Nextech Systems</t>
+          <t>endava</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, SQL Server, ELT, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0a946d2db71d280</t>
+          <t>https://www.indeed.com/viewjob?jk=163d2dba42ea7b46</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Engineer III, Platform Engineering</t>
+          <t>Salesforce Technical Architect, Data &amp; AI</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Omnicell</t>
+          <t>NeuraFlash, Part of Accenture</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cranberry Township, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Kubernetes, Git, CloudWatch</t>
+          <t>AWS, Redshift, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0ef9b73a4ad4b77</t>
+          <t>https://www.indeed.com/viewjob?jk=3420dddc661e222d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Senior Software Engineer, Data Trust</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=226e96da47ff2b1a</t>
+          <t>https://www.indeed.com/viewjob?jk=6704fd5656501c07</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Consultant – Data Engineer &amp; Governance</t>
+          <t>Sr. Programmer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Quisitive</t>
+          <t>COMMUNITY BEHAVIORAL HEALTH</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd77d29cb01573c</t>
+          <t>https://www.indeed.com/viewjob?jk=93628dfc1ed2e57f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer III (Platform)</t>
+          <t>SAS Developer (with Admin Background)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MAPFRE Insurance</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Webster, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, Scala, Data Modeling, ETL, CI/CD, Jenkins, Jenkins, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c94972b0ddefdba</t>
+          <t>https://www.indeed.com/viewjob?jk=f708bb2089c8e37e</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer - Finance Modernization</t>
+          <t>SAS Developer (with Admin Background)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Spark, Scala, CI/CD, Terraform, Git</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ee917ec6e025e8</t>
+          <t>https://www.indeed.com/viewjob?jk=2b030dd9a627fd2c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Programmer</t>
+          <t>Business Intelligence Developer - Analytics</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>COMMUNITY BEHAVIORAL HEALTH</t>
+          <t>EvergreenHealth</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Data Modeling, Star Schema, ETL, Power BI, Tableau, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93628dfc1ed2e57f</t>
+          <t>https://www.indeed.com/viewjob?jk=847c2fe533f1ec86</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Lakebase Sales Specialist</t>
+          <t>Sr. Software Engineer (React/Typescript)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Vertafore</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9c11c9c5d79b69</t>
+          <t>https://www.indeed.com/viewjob?jk=757afec97d5d27e0</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Machine Learning Engineer, Model Risk Management</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>endava</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, GCP, Vertex AI, Snowflake, ETL, MLflow, pytest, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163d2dba42ea7b46</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4b8c7a56e0e088</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Salesforce Technical Architect, Data &amp; AI</t>
+          <t>AI LLM Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NeuraFlash, Part of Accenture</t>
+          <t>Siemens Healthineers</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Redshift, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, Data Modeling, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3420dddc661e222d</t>
+          <t>https://www.indeed.com/viewjob?jk=77cc10c4736bb6e5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior DevOps/MLOps Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Algorized</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Campbell, CA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,287 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c88a8d02f220104</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Senior Specialist - Quality Engineering</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>LTIMindtree</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Splunk, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=53ced3da28996aca</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer, Model Risk Management</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Block</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, GCP, Vertex AI, Snowflake, ETL, MLflow, pytest, Git</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4b8c7a56e0e088</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>AI LLM Engineer</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Siemens Healthineers</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, Data Modeling, ELT, Power BI, Git, Python</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=77cc10c4736bb6e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>SAS Developer (with Admin Background)</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f708bb2089c8e37e</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>SAS Developer (with Admin Background)</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2b030dd9a627fd2c</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer - Analytics</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>EvergreenHealth</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Kirkland, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Data Modeling, Star Schema, ETL, Power BI, Tableau, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=847c2fe533f1ec86</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer (React/Typescript)</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Vertafore</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=757afec97d5d27e0</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Data Engineer - Java - Loops</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Copperleaf Technologies Inc.</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe4ff78e6fcedc19</t>
+          <t>https://www.indeed.com/viewjob?jk=b5ac532ab4d53203</t>
         </is>
       </c>
     </row>
